--- a/research/traditional_assets/database/data/austria/austria_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09934418964914585</v>
+        <v>0.09913996359398788</v>
       </c>
       <c r="C2">
-        <v>330.1497804132016</v>
+        <v>327.5032635887638</v>
       </c>
       <c r="D2">
-        <v>275.1497804132016</v>
+        <v>276.2032635887638</v>
       </c>
       <c r="E2">
-        <v>-154</v>
+        <v>-150.3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G2">
         <v>55</v>
@@ -1451,28 +1451,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.18611</v>
       </c>
       <c r="N2">
-        <v>49.99795918367347</v>
+        <v>49.81184918367347</v>
       </c>
       <c r="O2">
-        <v>11.99951020408163</v>
+        <v>11.95484380408163</v>
       </c>
       <c r="P2">
-        <v>37.99844897959184</v>
+        <v>37.85700537959184</v>
       </c>
       <c r="Q2">
-        <v>72.89844897959185</v>
+        <v>72.75700537959185</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09934418964914585</v>
+        <v>0.09975523595352312</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109376440074233</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>268.6473547024527</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09913996359398788</v>
+        <v>0.09893573753882993</v>
       </c>
       <c r="C3">
-        <v>327.5032635887638</v>
+        <v>324.864844843814</v>
       </c>
       <c r="D3">
-        <v>276.2032635887638</v>
+        <v>277.2648448438139</v>
       </c>
       <c r="E3">
-        <v>-150.3</v>
+        <v>-146.6</v>
       </c>
       <c r="F3">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="G3">
         <v>55</v>
@@ -1533,28 +1533,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M3">
-        <v>0.18611</v>
+        <v>0.37222</v>
       </c>
       <c r="N3">
-        <v>49.81184918367347</v>
+        <v>49.62573918367347</v>
       </c>
       <c r="O3">
-        <v>11.95484380408163</v>
+        <v>11.91017740408163</v>
       </c>
       <c r="P3">
-        <v>37.85700537959184</v>
+        <v>37.71556177959184</v>
       </c>
       <c r="Q3">
-        <v>72.75700537959185</v>
+        <v>72.61556177959184</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09975523595352312</v>
+        <v>0.1001746709579897</v>
       </c>
       <c r="T3">
-        <v>1.109376440074233</v>
+        <v>1.118000465229057</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>268.6473547024527</v>
+        <v>134.3236773512264</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09893573753882993</v>
+        <v>0.098731511483672</v>
       </c>
       <c r="C4">
-        <v>324.864844843814</v>
+        <v>322.2346179129978</v>
       </c>
       <c r="D4">
-        <v>277.2648448438139</v>
+        <v>278.3346179129978</v>
       </c>
       <c r="E4">
-        <v>-146.6</v>
+        <v>-142.9</v>
       </c>
       <c r="F4">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="G4">
         <v>55</v>
@@ -1615,28 +1615,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M4">
-        <v>0.37222</v>
+        <v>0.55833</v>
       </c>
       <c r="N4">
-        <v>49.62573918367347</v>
+        <v>49.43962918367347</v>
       </c>
       <c r="O4">
-        <v>11.91017740408163</v>
+        <v>11.86551100408163</v>
       </c>
       <c r="P4">
-        <v>37.71556177959184</v>
+        <v>37.57411817959184</v>
       </c>
       <c r="Q4">
-        <v>72.61556177959184</v>
+        <v>72.47411817959184</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1001746709579897</v>
+        <v>0.1006027541068784</v>
       </c>
       <c r="T4">
-        <v>1.118000465229057</v>
+        <v>1.126802305335528</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>134.3236773512264</v>
+        <v>89.54911823415091</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.098731511483672</v>
+        <v>0.09852728542851404</v>
       </c>
       <c r="C5">
-        <v>322.2346179129978</v>
+        <v>319.6126779831931</v>
       </c>
       <c r="D5">
-        <v>278.3346179129978</v>
+        <v>279.4126779831931</v>
       </c>
       <c r="E5">
-        <v>-142.9</v>
+        <v>-139.2</v>
       </c>
       <c r="F5">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="G5">
         <v>55</v>
@@ -1697,28 +1697,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M5">
-        <v>0.55833</v>
+        <v>0.74444</v>
       </c>
       <c r="N5">
-        <v>49.43962918367347</v>
+        <v>49.25351918367348</v>
       </c>
       <c r="O5">
-        <v>11.86551100408163</v>
+        <v>11.82084460408163</v>
       </c>
       <c r="P5">
-        <v>37.57411817959184</v>
+        <v>37.43267457959184</v>
       </c>
       <c r="Q5">
-        <v>72.47411817959184</v>
+        <v>72.33267457959184</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1006027541068784</v>
+        <v>0.1010397556547021</v>
       </c>
       <c r="T5">
-        <v>1.126802305335528</v>
+        <v>1.135787517110884</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>89.54911823415091</v>
+        <v>67.16183867561318</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09852728542851404</v>
+        <v>0.09832305937335609</v>
       </c>
       <c r="C6">
-        <v>319.6126779831931</v>
+        <v>316.9991217217422</v>
       </c>
       <c r="D6">
-        <v>279.4126779831931</v>
+        <v>280.4991217217422</v>
       </c>
       <c r="E6">
-        <v>-139.2</v>
+        <v>-135.5</v>
       </c>
       <c r="F6">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="G6">
         <v>55</v>
@@ -1779,28 +1779,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M6">
-        <v>0.74444</v>
+        <v>0.93055</v>
       </c>
       <c r="N6">
-        <v>49.25351918367348</v>
+        <v>49.06740918367348</v>
       </c>
       <c r="O6">
-        <v>11.82084460408163</v>
+        <v>11.77617820408163</v>
       </c>
       <c r="P6">
-        <v>37.43267457959184</v>
+        <v>37.29123097959184</v>
       </c>
       <c r="Q6">
-        <v>72.33267457959184</v>
+        <v>72.19123097959185</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1010397556547021</v>
+        <v>0.1014859572351117</v>
       </c>
       <c r="T6">
-        <v>1.135787517110884</v>
+        <v>1.144961891239404</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.16183867561318</v>
+        <v>53.72947094049054</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09832305937335609</v>
+        <v>0.09811883331819814</v>
       </c>
       <c r="C7">
-        <v>316.9991217217422</v>
+        <v>314.394047305348</v>
       </c>
       <c r="D7">
-        <v>280.4991217217422</v>
+        <v>281.594047305348</v>
       </c>
       <c r="E7">
-        <v>-135.5</v>
+        <v>-131.8</v>
       </c>
       <c r="F7">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="G7">
         <v>55</v>
@@ -1861,28 +1861,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M7">
-        <v>0.93055</v>
+        <v>1.11666</v>
       </c>
       <c r="N7">
-        <v>49.06740918367348</v>
+        <v>48.88129918367347</v>
       </c>
       <c r="O7">
-        <v>11.77617820408163</v>
+        <v>11.73151180408163</v>
       </c>
       <c r="P7">
-        <v>37.29123097959184</v>
+        <v>37.14978737959184</v>
       </c>
       <c r="Q7">
-        <v>72.19123097959185</v>
+        <v>72.04978737959183</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1014859572351117</v>
+        <v>0.1019416524661682</v>
       </c>
       <c r="T7">
-        <v>1.144961891239404</v>
+        <v>1.154331464817468</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.72947094049054</v>
+        <v>44.77455911707545</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09811883331819814</v>
+        <v>0.0979146072630402</v>
       </c>
       <c r="C8">
-        <v>314.394047305348</v>
+        <v>311.7975544496475</v>
       </c>
       <c r="D8">
-        <v>281.594047305348</v>
+        <v>282.6975544496475</v>
       </c>
       <c r="E8">
-        <v>-131.8</v>
+        <v>-128.1</v>
       </c>
       <c r="F8">
-        <v>22.2</v>
+        <v>25.9</v>
       </c>
       <c r="G8">
         <v>55</v>
@@ -1943,28 +1943,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M8">
-        <v>1.11666</v>
+        <v>1.30277</v>
       </c>
       <c r="N8">
-        <v>48.88129918367347</v>
+        <v>48.69518918367347</v>
       </c>
       <c r="O8">
-        <v>11.73151180408163</v>
+        <v>11.68684540408163</v>
       </c>
       <c r="P8">
-        <v>37.14978737959184</v>
+        <v>37.00834377959184</v>
       </c>
       <c r="Q8">
-        <v>72.04978737959183</v>
+        <v>71.90834377959185</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1019416524661682</v>
+        <v>0.1024071475946669</v>
       </c>
       <c r="T8">
-        <v>1.154331464817468</v>
+        <v>1.163902534601512</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.77455911707545</v>
+        <v>38.37819352892182</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09791460726304019</v>
+        <v>0.09771038120788224</v>
       </c>
       <c r="C9">
-        <v>311.7975544496476</v>
+        <v>309.209744439485</v>
       </c>
       <c r="D9">
-        <v>282.6975544496476</v>
+        <v>283.809744439485</v>
       </c>
       <c r="E9">
-        <v>-128.1</v>
+        <v>-124.4</v>
       </c>
       <c r="F9">
-        <v>25.9</v>
+        <v>29.6</v>
       </c>
       <c r="G9">
         <v>55</v>
@@ -2025,28 +2025,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M9">
-        <v>1.30277</v>
+        <v>1.48888</v>
       </c>
       <c r="N9">
-        <v>48.69518918367347</v>
+        <v>48.50907918367347</v>
       </c>
       <c r="O9">
-        <v>11.68684540408163</v>
+        <v>11.64217900408163</v>
       </c>
       <c r="P9">
-        <v>37.00834377959184</v>
+        <v>36.86690017959184</v>
       </c>
       <c r="Q9">
-        <v>71.90834377959185</v>
+        <v>71.76690017959184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1024071475946669</v>
+        <v>0.1028827621824807</v>
       </c>
       <c r="T9">
-        <v>1.163902534601512</v>
+        <v>1.173681671119991</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.37819352892181</v>
+        <v>33.58091933780658</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09771038120788224</v>
+        <v>0.0975061551527243</v>
       </c>
       <c r="C10">
-        <v>309.209744439485</v>
+        <v>306.6307201599008</v>
       </c>
       <c r="D10">
-        <v>283.809744439485</v>
+        <v>284.9307201599008</v>
       </c>
       <c r="E10">
-        <v>-124.4</v>
+        <v>-120.7</v>
       </c>
       <c r="F10">
-        <v>29.6</v>
+        <v>33.3</v>
       </c>
       <c r="G10">
         <v>55</v>
@@ -2107,28 +2107,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M10">
-        <v>1.48888</v>
+        <v>1.67499</v>
       </c>
       <c r="N10">
-        <v>48.50907918367347</v>
+        <v>48.32296918367347</v>
       </c>
       <c r="O10">
-        <v>11.64217900408163</v>
+        <v>11.59751260408163</v>
       </c>
       <c r="P10">
-        <v>36.86690017959184</v>
+        <v>36.72545657959184</v>
       </c>
       <c r="Q10">
-        <v>71.76690017959184</v>
+        <v>71.62545657959184</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1028827621824807</v>
+        <v>0.1033688298381586</v>
       </c>
       <c r="T10">
-        <v>1.173681671119991</v>
+        <v>1.1836757337158</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.58091933780658</v>
+        <v>29.8497060780503</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0975061551527243</v>
+        <v>0.09730192909756635</v>
       </c>
       <c r="C11">
-        <v>306.6307201599008</v>
+        <v>304.0605861278597</v>
       </c>
       <c r="D11">
-        <v>284.9307201599008</v>
+        <v>286.0605861278597</v>
       </c>
       <c r="E11">
-        <v>-120.7</v>
+        <v>-117</v>
       </c>
       <c r="F11">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>55</v>
@@ -2189,28 +2189,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M11">
-        <v>1.67499</v>
+        <v>1.8611</v>
       </c>
       <c r="N11">
-        <v>48.32296918367347</v>
+        <v>48.13685918367347</v>
       </c>
       <c r="O11">
-        <v>11.59751260408163</v>
+        <v>11.55284620408163</v>
       </c>
       <c r="P11">
-        <v>36.72545657959184</v>
+        <v>36.58401297959184</v>
       </c>
       <c r="Q11">
-        <v>71.62545657959184</v>
+        <v>71.48401297959185</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1033688298381586</v>
+        <v>0.1038656989972959</v>
       </c>
       <c r="T11">
-        <v>1.1836757337158</v>
+        <v>1.193891886591516</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.8497060780503</v>
+        <v>26.86473547024527</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09730192909756635</v>
+        <v>0.09709770304240839</v>
       </c>
       <c r="C12">
-        <v>304.0605861278597</v>
+        <v>301.4994485247349</v>
       </c>
       <c r="D12">
-        <v>286.0605861278597</v>
+        <v>287.1994485247349</v>
       </c>
       <c r="E12">
-        <v>-117</v>
+        <v>-113.3</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>40.7</v>
       </c>
       <c r="G12">
         <v>55</v>
@@ -2271,28 +2271,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M12">
-        <v>1.8611</v>
+        <v>2.04721</v>
       </c>
       <c r="N12">
-        <v>48.13685918367347</v>
+        <v>47.95074918367347</v>
       </c>
       <c r="O12">
-        <v>11.55284620408163</v>
+        <v>11.50817980408163</v>
       </c>
       <c r="P12">
-        <v>36.58401297959184</v>
+        <v>36.44256937959184</v>
       </c>
       <c r="Q12">
-        <v>71.48401297959185</v>
+        <v>71.34256937959185</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1038656989972959</v>
+        <v>0.104373733755515</v>
       </c>
       <c r="T12">
-        <v>1.193891886591516</v>
+        <v>1.204337615936348</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.86473547024527</v>
+        <v>24.42248679113206</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09709770304240839</v>
+        <v>0.09689347698725044</v>
       </c>
       <c r="C13">
-        <v>301.4994485247349</v>
+        <v>298.9474152295724</v>
       </c>
       <c r="D13">
-        <v>287.1994485247349</v>
+        <v>288.3474152295723</v>
       </c>
       <c r="E13">
-        <v>-113.3</v>
+        <v>-109.6</v>
       </c>
       <c r="F13">
-        <v>40.7</v>
+        <v>44.4</v>
       </c>
       <c r="G13">
         <v>55</v>
@@ -2353,28 +2353,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M13">
-        <v>2.04721</v>
+        <v>2.23332</v>
       </c>
       <c r="N13">
-        <v>47.95074918367347</v>
+        <v>47.76463918367347</v>
       </c>
       <c r="O13">
-        <v>11.50817980408163</v>
+        <v>11.46351340408163</v>
       </c>
       <c r="P13">
-        <v>36.44256937959184</v>
+        <v>36.30112577959184</v>
       </c>
       <c r="Q13">
-        <v>71.34256937959185</v>
+        <v>71.20112577959185</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.104373733755515</v>
+        <v>0.1048933147582391</v>
       </c>
       <c r="T13">
-        <v>1.204337615936348</v>
+        <v>1.215020748220836</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.42248679113206</v>
+        <v>22.38727955853773</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09689347698725044</v>
+        <v>0.09668925093209249</v>
       </c>
       <c r="C14">
-        <v>298.9474152295724</v>
+        <v>296.4045958531564</v>
       </c>
       <c r="D14">
-        <v>288.3474152295723</v>
+        <v>289.5045958531564</v>
       </c>
       <c r="E14">
-        <v>-109.6</v>
+        <v>-105.9</v>
       </c>
       <c r="F14">
-        <v>44.4</v>
+        <v>48.1</v>
       </c>
       <c r="G14">
         <v>55</v>
@@ -2435,28 +2435,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M14">
-        <v>2.23332</v>
+        <v>2.41943</v>
       </c>
       <c r="N14">
-        <v>47.76463918367347</v>
+        <v>47.57852918367347</v>
       </c>
       <c r="O14">
-        <v>11.46351340408163</v>
+        <v>11.41884700408163</v>
       </c>
       <c r="P14">
-        <v>36.30112577959184</v>
+        <v>36.15968217959184</v>
       </c>
       <c r="Q14">
-        <v>71.20112577959185</v>
+        <v>71.05968217959185</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1048933147582391</v>
+        <v>0.1054248401518305</v>
       </c>
       <c r="T14">
-        <v>1.215020748220836</v>
+        <v>1.225949469753244</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.38727955853773</v>
+        <v>20.6651811309579</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09668925093209249</v>
+        <v>0.09648502487693454</v>
       </c>
       <c r="C15">
-        <v>296.4045958531564</v>
+        <v>293.8711017728979</v>
       </c>
       <c r="D15">
-        <v>289.5045958531564</v>
+        <v>290.6711017728979</v>
       </c>
       <c r="E15">
-        <v>-105.9</v>
+        <v>-102.2</v>
       </c>
       <c r="F15">
-        <v>48.1</v>
+        <v>51.8</v>
       </c>
       <c r="G15">
         <v>55</v>
@@ -2517,28 +2517,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M15">
-        <v>2.41943</v>
+        <v>2.60554</v>
       </c>
       <c r="N15">
-        <v>47.57852918367347</v>
+        <v>47.39241918367347</v>
       </c>
       <c r="O15">
-        <v>11.41884700408163</v>
+        <v>11.37418060408163</v>
       </c>
       <c r="P15">
-        <v>36.15968217959184</v>
+        <v>36.01823857959184</v>
       </c>
       <c r="Q15">
-        <v>71.05968217959185</v>
+        <v>70.91823857959184</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1054248401518305</v>
+        <v>0.1059687266010867</v>
       </c>
       <c r="T15">
-        <v>1.225949469753244</v>
+        <v>1.237132347600358</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.6651811309579</v>
+        <v>19.18909676446091</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09648502487693454</v>
+        <v>0.09628079882177659</v>
       </c>
       <c r="C16">
-        <v>293.8711017728979</v>
+        <v>291.3470461685695</v>
       </c>
       <c r="D16">
-        <v>290.6711017728979</v>
+        <v>291.8470461685695</v>
       </c>
       <c r="E16">
-        <v>-102.2</v>
+        <v>-98.5</v>
       </c>
       <c r="F16">
-        <v>51.8</v>
+        <v>55.50000000000001</v>
       </c>
       <c r="G16">
         <v>55</v>
@@ -2599,28 +2599,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M16">
-        <v>2.60554</v>
+        <v>2.79165</v>
       </c>
       <c r="N16">
-        <v>47.39241918367347</v>
+        <v>47.20630918367348</v>
       </c>
       <c r="O16">
-        <v>11.37418060408163</v>
+        <v>11.32951420408163</v>
       </c>
       <c r="P16">
-        <v>36.01823857959184</v>
+        <v>35.87679497959184</v>
       </c>
       <c r="Q16">
-        <v>70.91823857959184</v>
+        <v>70.77679497959184</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1059687266010867</v>
+        <v>0.1065254103785607</v>
       </c>
       <c r="T16">
-        <v>1.237132347600358</v>
+        <v>1.248578351985052</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.18909676446091</v>
+        <v>17.90982364683018</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09628079882177659</v>
+        <v>0.09607657276661864</v>
       </c>
       <c r="C17">
-        <v>291.3470461685695</v>
+        <v>288.8325440589126</v>
       </c>
       <c r="D17">
-        <v>291.8470461685695</v>
+        <v>293.0325440589126</v>
       </c>
       <c r="E17">
-        <v>-98.5</v>
+        <v>-94.8</v>
       </c>
       <c r="F17">
-        <v>55.5</v>
+        <v>59.2</v>
       </c>
       <c r="G17">
         <v>55</v>
@@ -2681,28 +2681,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M17">
-        <v>2.79165</v>
+        <v>2.97776</v>
       </c>
       <c r="N17">
-        <v>47.20630918367348</v>
+        <v>47.02019918367347</v>
       </c>
       <c r="O17">
-        <v>11.32951420408163</v>
+        <v>11.28484780408163</v>
       </c>
       <c r="P17">
-        <v>35.87679497959184</v>
+        <v>35.73535137959183</v>
       </c>
       <c r="Q17">
-        <v>70.77679497959184</v>
+        <v>70.63535137959184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1065254103785607</v>
+        <v>0.1070953485316889</v>
       </c>
       <c r="T17">
-        <v>1.248578351985052</v>
+        <v>1.260296880283667</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.90982364683018</v>
+        <v>16.7904596689033</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09607657276661864</v>
+        <v>0.09587234671146069</v>
       </c>
       <c r="C18">
-        <v>288.8325440589126</v>
+        <v>286.3277123391392</v>
       </c>
       <c r="D18">
-        <v>293.0325440589126</v>
+        <v>294.2277123391393</v>
       </c>
       <c r="E18">
-        <v>-94.8</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="F18">
-        <v>59.2</v>
+        <v>62.90000000000001</v>
       </c>
       <c r="G18">
         <v>55</v>
@@ -2763,28 +2763,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M18">
-        <v>2.97776</v>
+        <v>3.16387</v>
       </c>
       <c r="N18">
-        <v>47.02019918367347</v>
+        <v>46.83408918367347</v>
       </c>
       <c r="O18">
-        <v>11.28484780408163</v>
+        <v>11.24018140408163</v>
       </c>
       <c r="P18">
-        <v>35.73535137959183</v>
+        <v>35.59390777959184</v>
       </c>
       <c r="Q18">
-        <v>70.63535137959184</v>
+        <v>70.49390777959184</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1070953485316889</v>
+        <v>0.10767902013429</v>
       </c>
       <c r="T18">
-        <v>1.260296880283667</v>
+        <v>1.272297782758152</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.7904596689033</v>
+        <v>15.80278557073251</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09587234671146069</v>
+        <v>0.09566812065630276</v>
       </c>
       <c r="C19">
-        <v>286.3277123391392</v>
+        <v>283.8326698193561</v>
       </c>
       <c r="D19">
-        <v>294.2277123391393</v>
+        <v>295.4326698193561</v>
       </c>
       <c r="E19">
-        <v>-91.09999999999999</v>
+        <v>-87.39999999999999</v>
       </c>
       <c r="F19">
-        <v>62.90000000000001</v>
+        <v>66.60000000000001</v>
       </c>
       <c r="G19">
         <v>55</v>
@@ -2845,28 +2845,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M19">
-        <v>3.16387</v>
+        <v>3.34998</v>
       </c>
       <c r="N19">
-        <v>46.83408918367347</v>
+        <v>46.64797918367347</v>
       </c>
       <c r="O19">
-        <v>11.24018140408163</v>
+        <v>11.19551500408163</v>
       </c>
       <c r="P19">
-        <v>35.59390777959184</v>
+        <v>35.45246417959184</v>
       </c>
       <c r="Q19">
-        <v>70.49390777959184</v>
+        <v>70.35246417959183</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.10767902013429</v>
+        <v>0.1082769276296375</v>
       </c>
       <c r="T19">
-        <v>1.272297782758152</v>
+        <v>1.284591390171039</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.80278557073251</v>
+        <v>14.92485303902515</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09566812065630274</v>
+        <v>0.09546389460114479</v>
       </c>
       <c r="C20">
-        <v>283.8326698193562</v>
+        <v>281.3475372639363</v>
       </c>
       <c r="D20">
-        <v>295.4326698193561</v>
+        <v>296.6475372639363</v>
       </c>
       <c r="E20">
-        <v>-87.40000000000001</v>
+        <v>-83.7</v>
       </c>
       <c r="F20">
-        <v>66.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G20">
         <v>55</v>
@@ -2927,28 +2927,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M20">
-        <v>3.34998</v>
+        <v>3.53609</v>
       </c>
       <c r="N20">
-        <v>46.64797918367347</v>
+        <v>46.46186918367347</v>
       </c>
       <c r="O20">
-        <v>11.19551500408163</v>
+        <v>11.15084860408163</v>
       </c>
       <c r="P20">
-        <v>35.45246417959184</v>
+        <v>35.31102057959184</v>
       </c>
       <c r="Q20">
-        <v>70.35246417959183</v>
+        <v>70.21102057959185</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1082769276296375</v>
+        <v>0.1088895982730183</v>
       </c>
       <c r="T20">
-        <v>1.284591390171039</v>
+        <v>1.297188543445973</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.92485303902515</v>
+        <v>14.13933445802383</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09546389460114479</v>
+        <v>0.09525966854598684</v>
       </c>
       <c r="C21">
-        <v>281.3475372639363</v>
+        <v>278.8724374318661</v>
       </c>
       <c r="D21">
-        <v>296.6475372639363</v>
+        <v>297.8724374318661</v>
       </c>
       <c r="E21">
-        <v>-83.7</v>
+        <v>-80</v>
       </c>
       <c r="F21">
-        <v>70.3</v>
+        <v>74</v>
       </c>
       <c r="G21">
         <v>55</v>
@@ -3009,28 +3009,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M21">
-        <v>3.53609</v>
+        <v>3.7222</v>
       </c>
       <c r="N21">
-        <v>46.46186918367347</v>
+        <v>46.27575918367347</v>
       </c>
       <c r="O21">
-        <v>11.15084860408163</v>
+        <v>11.10618220408163</v>
       </c>
       <c r="P21">
-        <v>35.31102057959184</v>
+        <v>35.16957697959184</v>
       </c>
       <c r="Q21">
-        <v>70.21102057959185</v>
+        <v>70.06957697959184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1088895982730183</v>
+        <v>0.1095175856824835</v>
       </c>
       <c r="T21">
-        <v>1.297188543445973</v>
+        <v>1.31010062555278</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.13933445802383</v>
+        <v>13.43236773512264</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09525966854598684</v>
+        <v>0.0952948424908289</v>
       </c>
       <c r="C22">
-        <v>278.8724374318661</v>
+        <v>274.9607517661094</v>
       </c>
       <c r="D22">
-        <v>297.8724374318661</v>
+        <v>297.6607517661094</v>
       </c>
       <c r="E22">
-        <v>-80</v>
+        <v>-76.3</v>
       </c>
       <c r="F22">
-        <v>74</v>
+        <v>77.7</v>
       </c>
       <c r="G22">
         <v>55</v>
@@ -3091,45 +3091,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M22">
-        <v>3.7222</v>
+        <v>4.02486</v>
       </c>
       <c r="N22">
-        <v>46.27575918367347</v>
+        <v>45.97309918367347</v>
       </c>
       <c r="O22">
-        <v>11.10618220408163</v>
+        <v>11.03354380408163</v>
       </c>
       <c r="P22">
-        <v>35.16957697959184</v>
+        <v>34.93955537959184</v>
       </c>
       <c r="Q22">
-        <v>70.06957697959184</v>
+        <v>69.83955537959184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1095175856824835</v>
+        <v>0.1101614715073783</v>
       </c>
       <c r="T22">
-        <v>1.31010062555278</v>
+        <v>1.32333959581419</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.43236773512264</v>
+        <v>12.42228529282347</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0952948424908289</v>
+        <v>0.09510201643567096</v>
       </c>
       <c r="C23">
-        <v>274.9607517661094</v>
+        <v>272.4249383995972</v>
       </c>
       <c r="D23">
-        <v>297.6607517661094</v>
+        <v>298.8249383995972</v>
       </c>
       <c r="E23">
-        <v>-76.3</v>
+        <v>-72.59999999999999</v>
       </c>
       <c r="F23">
-        <v>77.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G23">
         <v>55</v>
@@ -3173,28 +3173,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M23">
-        <v>4.02486</v>
+        <v>4.21652</v>
       </c>
       <c r="N23">
-        <v>45.97309918367347</v>
+        <v>45.78143918367347</v>
       </c>
       <c r="O23">
-        <v>11.03354380408163</v>
+        <v>10.98754540408163</v>
       </c>
       <c r="P23">
-        <v>34.93955537959184</v>
+        <v>34.79389377959184</v>
       </c>
       <c r="Q23">
-        <v>69.83955537959184</v>
+        <v>69.69389377959185</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1101614715073783</v>
+        <v>0.1108218672252192</v>
       </c>
       <c r="T23">
-        <v>1.32333959581419</v>
+        <v>1.336918026851533</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.42228529282347</v>
+        <v>11.85763596133149</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09510201643567096</v>
+        <v>0.09490919038051301</v>
       </c>
       <c r="C24">
-        <v>272.4249383995972</v>
+        <v>269.8982673347301</v>
       </c>
       <c r="D24">
-        <v>298.8249383995972</v>
+        <v>299.9982673347301</v>
       </c>
       <c r="E24">
-        <v>-72.59999999999999</v>
+        <v>-68.89999999999999</v>
       </c>
       <c r="F24">
-        <v>81.40000000000001</v>
+        <v>85.10000000000001</v>
       </c>
       <c r="G24">
         <v>55</v>
@@ -3255,28 +3255,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M24">
-        <v>4.21652</v>
+        <v>4.408180000000001</v>
       </c>
       <c r="N24">
-        <v>45.78143918367347</v>
+        <v>45.58977918367347</v>
       </c>
       <c r="O24">
-        <v>10.98754540408163</v>
+        <v>10.94154700408163</v>
       </c>
       <c r="P24">
-        <v>34.79389377959184</v>
+        <v>34.64823217959184</v>
       </c>
       <c r="Q24">
-        <v>69.69389377959185</v>
+        <v>69.54823217959185</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1108218672252192</v>
+        <v>0.1114994160785883</v>
       </c>
       <c r="T24">
-        <v>1.336918026851533</v>
+        <v>1.350849144409327</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.85763596133149</v>
+        <v>11.34208657170838</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09490919038051301</v>
+        <v>0.09471636432535505</v>
       </c>
       <c r="C25">
-        <v>269.8982673347301</v>
+        <v>267.3808466871044</v>
       </c>
       <c r="D25">
-        <v>299.9982673347301</v>
+        <v>301.1808466871044</v>
       </c>
       <c r="E25">
-        <v>-68.89999999999999</v>
+        <v>-65.19999999999999</v>
       </c>
       <c r="F25">
-        <v>85.10000000000001</v>
+        <v>88.80000000000001</v>
       </c>
       <c r="G25">
         <v>55</v>
@@ -3337,28 +3337,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M25">
-        <v>4.408180000000001</v>
+        <v>4.59984</v>
       </c>
       <c r="N25">
-        <v>45.58977918367347</v>
+        <v>45.39811918367347</v>
       </c>
       <c r="O25">
-        <v>10.94154700408163</v>
+        <v>10.89554860408163</v>
       </c>
       <c r="P25">
-        <v>34.64823217959184</v>
+        <v>34.50257057959184</v>
       </c>
       <c r="Q25">
-        <v>69.54823217959185</v>
+        <v>69.40257057959184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1114994160785883</v>
+        <v>0.1121947951649409</v>
       </c>
       <c r="T25">
-        <v>1.350849144409327</v>
+        <v>1.365146870323905</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.34208657170838</v>
+        <v>10.86949963122053</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09471636432535505</v>
+        <v>0.09452353827019709</v>
       </c>
       <c r="C26">
-        <v>267.3808466871044</v>
+        <v>264.8727862838092</v>
       </c>
       <c r="D26">
-        <v>301.1808466871044</v>
+        <v>302.3727862838092</v>
       </c>
       <c r="E26">
-        <v>-65.2</v>
+        <v>-61.5</v>
       </c>
       <c r="F26">
-        <v>88.8</v>
+        <v>92.5</v>
       </c>
       <c r="G26">
         <v>55</v>
@@ -3419,28 +3419,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M26">
-        <v>4.599839999999999</v>
+        <v>4.7915</v>
       </c>
       <c r="N26">
-        <v>45.39811918367347</v>
+        <v>45.20645918367347</v>
       </c>
       <c r="O26">
-        <v>10.89554860408163</v>
+        <v>10.84955020408163</v>
       </c>
       <c r="P26">
-        <v>34.50257057959184</v>
+        <v>34.35690897959184</v>
       </c>
       <c r="Q26">
-        <v>69.40257057959184</v>
+        <v>69.25690897959184</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1121947951649409</v>
+        <v>0.1129087176935961</v>
       </c>
       <c r="T26">
-        <v>1.365146870323905</v>
+        <v>1.379825868929539</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.86949963122054</v>
+        <v>10.43471964597171</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09452353827019709</v>
+        <v>0.09433071221503914</v>
       </c>
       <c r="C27">
-        <v>264.8727862838092</v>
+        <v>262.3741976974286</v>
       </c>
       <c r="D27">
-        <v>302.3727862838092</v>
+        <v>303.5741976974286</v>
       </c>
       <c r="E27">
-        <v>-61.5</v>
+        <v>-57.8</v>
       </c>
       <c r="F27">
-        <v>92.5</v>
+        <v>96.2</v>
       </c>
       <c r="G27">
         <v>55</v>
@@ -3501,28 +3501,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M27">
-        <v>4.7915</v>
+        <v>4.98316</v>
       </c>
       <c r="N27">
-        <v>45.20645918367347</v>
+        <v>45.01479918367347</v>
       </c>
       <c r="O27">
-        <v>10.84955020408163</v>
+        <v>10.80355180408163</v>
       </c>
       <c r="P27">
-        <v>34.35690897959184</v>
+        <v>34.21124737959184</v>
       </c>
       <c r="Q27">
-        <v>69.25690897959184</v>
+        <v>69.11124737959184</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1129087176935961</v>
+        <v>0.1136419354257286</v>
       </c>
       <c r="T27">
-        <v>1.379825868929539</v>
+        <v>1.394901597227216</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.43471964597171</v>
+        <v>10.0333842749728</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09433071221503914</v>
+        <v>0.09448672615988118</v>
       </c>
       <c r="C28">
-        <v>262.3741976974286</v>
+        <v>257.7014108236613</v>
       </c>
       <c r="D28">
-        <v>303.5741976974286</v>
+        <v>302.6014108236612</v>
       </c>
       <c r="E28">
-        <v>-57.8</v>
+        <v>-54.09999999999999</v>
       </c>
       <c r="F28">
-        <v>96.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G28">
         <v>55</v>
@@ -3583,45 +3583,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M28">
-        <v>4.98316</v>
+        <v>5.344650000000001</v>
       </c>
       <c r="N28">
-        <v>45.01479918367347</v>
+        <v>44.65330918367347</v>
       </c>
       <c r="O28">
-        <v>10.80355180408163</v>
+        <v>10.71679420408163</v>
       </c>
       <c r="P28">
-        <v>34.21124737959184</v>
+        <v>33.93651497959183</v>
       </c>
       <c r="Q28">
-        <v>69.11124737959184</v>
+        <v>68.83651497959184</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1136419354257286</v>
+        <v>0.1143952413149057</v>
       </c>
       <c r="T28">
-        <v>1.394901597227216</v>
+        <v>1.410390359176885</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.0333842749728</v>
+        <v>9.354767699226977</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09448672615988118</v>
+        <v>0.09430682010472324</v>
       </c>
       <c r="C29">
-        <v>257.7014108236613</v>
+        <v>255.1237236446003</v>
       </c>
       <c r="D29">
-        <v>302.6014108236612</v>
+        <v>303.7237236446003</v>
       </c>
       <c r="E29">
-        <v>-54.09999999999999</v>
+        <v>-50.39999999999999</v>
       </c>
       <c r="F29">
-        <v>99.90000000000001</v>
+        <v>103.6</v>
       </c>
       <c r="G29">
         <v>55</v>
@@ -3665,28 +3665,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M29">
-        <v>5.344650000000001</v>
+        <v>5.5426</v>
       </c>
       <c r="N29">
-        <v>44.65330918367347</v>
+        <v>44.45535918367347</v>
       </c>
       <c r="O29">
-        <v>10.71679420408163</v>
+        <v>10.66928620408163</v>
       </c>
       <c r="P29">
-        <v>33.93651497959183</v>
+        <v>33.78607297959184</v>
       </c>
       <c r="Q29">
-        <v>68.83651497959184</v>
+        <v>68.68607297959184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1143952413149057</v>
+        <v>0.1151694723676712</v>
       </c>
       <c r="T29">
-        <v>1.410390359176885</v>
+        <v>1.426309364514044</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.354767699226977</v>
+        <v>9.020668852826015</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09430682010472324</v>
+        <v>0.0941269140495653</v>
       </c>
       <c r="C30">
-        <v>255.1237236446003</v>
+        <v>252.5543925079739</v>
       </c>
       <c r="D30">
-        <v>303.7237236446003</v>
+        <v>304.854392507974</v>
       </c>
       <c r="E30">
-        <v>-50.39999999999999</v>
+        <v>-46.69999999999999</v>
       </c>
       <c r="F30">
-        <v>103.6</v>
+        <v>107.3</v>
       </c>
       <c r="G30">
         <v>55</v>
@@ -3747,28 +3747,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M30">
-        <v>5.5426</v>
+        <v>5.740550000000001</v>
       </c>
       <c r="N30">
-        <v>44.45535918367347</v>
+        <v>44.25740918367347</v>
       </c>
       <c r="O30">
-        <v>10.66928620408163</v>
+        <v>10.62177820408163</v>
       </c>
       <c r="P30">
-        <v>33.78607297959184</v>
+        <v>33.63563097959184</v>
       </c>
       <c r="Q30">
-        <v>68.68607297959184</v>
+        <v>68.53563097959184</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1151694723676712</v>
+        <v>0.1159655127458666</v>
       </c>
       <c r="T30">
-        <v>1.426309364514044</v>
+        <v>1.442676792536758</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.020668852826015</v>
+        <v>8.709611306176843</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0941269140495653</v>
+        <v>0.09394700799440733</v>
       </c>
       <c r="C31">
-        <v>252.5543925079739</v>
+        <v>249.9935110833185</v>
       </c>
       <c r="D31">
-        <v>304.854392507974</v>
+        <v>305.9935110833185</v>
       </c>
       <c r="E31">
-        <v>-46.7</v>
+        <v>-43</v>
       </c>
       <c r="F31">
-        <v>107.3</v>
+        <v>111</v>
       </c>
       <c r="G31">
         <v>55</v>
@@ -3829,28 +3829,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M31">
-        <v>5.74055</v>
+        <v>5.938499999999999</v>
       </c>
       <c r="N31">
-        <v>44.25740918367347</v>
+        <v>44.05945918367348</v>
       </c>
       <c r="O31">
-        <v>10.62177820408163</v>
+        <v>10.57427020408163</v>
       </c>
       <c r="P31">
-        <v>33.63563097959184</v>
+        <v>33.48518897959184</v>
       </c>
       <c r="Q31">
-        <v>68.53563097959184</v>
+        <v>68.38518897959185</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1159655127458666</v>
+        <v>0.1167842971348676</v>
       </c>
       <c r="T31">
-        <v>1.442676792536758</v>
+        <v>1.45951186136012</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.709611306176843</v>
+        <v>8.419290929304282</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09394700799440733</v>
+        <v>0.09376710193924939</v>
       </c>
       <c r="C32">
-        <v>249.9935110833185</v>
+        <v>247.4411744454421</v>
       </c>
       <c r="D32">
-        <v>305.9935110833185</v>
+        <v>307.1411744454421</v>
       </c>
       <c r="E32">
-        <v>-43</v>
+        <v>-39.3</v>
       </c>
       <c r="F32">
-        <v>111</v>
+        <v>114.7</v>
       </c>
       <c r="G32">
         <v>55</v>
@@ -3911,28 +3911,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M32">
-        <v>5.938499999999999</v>
+        <v>6.13645</v>
       </c>
       <c r="N32">
-        <v>44.05945918367348</v>
+        <v>43.86150918367348</v>
       </c>
       <c r="O32">
-        <v>10.57427020408163</v>
+        <v>10.52676220408163</v>
       </c>
       <c r="P32">
-        <v>33.48518897959184</v>
+        <v>33.33474697959184</v>
       </c>
       <c r="Q32">
-        <v>68.38518897959185</v>
+        <v>68.23474697959185</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1167842971348676</v>
+        <v>0.1176268144047093</v>
       </c>
       <c r="T32">
-        <v>1.45951186136012</v>
+        <v>1.476834903192855</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.419290929304282</v>
+        <v>8.147700899326725</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09376710193924939</v>
+        <v>0.09358719588409144</v>
       </c>
       <c r="C33">
-        <v>247.4411744454421</v>
+        <v>244.8974791008792</v>
       </c>
       <c r="D33">
-        <v>307.1411744454421</v>
+        <v>308.2974791008792</v>
       </c>
       <c r="E33">
-        <v>-39.3</v>
+        <v>-35.59999999999999</v>
       </c>
       <c r="F33">
-        <v>114.7</v>
+        <v>118.4</v>
       </c>
       <c r="G33">
         <v>55</v>
@@ -3993,28 +3993,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M33">
-        <v>6.13645</v>
+        <v>6.3344</v>
       </c>
       <c r="N33">
-        <v>43.86150918367348</v>
+        <v>43.66355918367347</v>
       </c>
       <c r="O33">
-        <v>10.52676220408163</v>
+        <v>10.47925420408163</v>
       </c>
       <c r="P33">
-        <v>33.33474697959184</v>
+        <v>33.18430497959184</v>
       </c>
       <c r="Q33">
-        <v>68.23474697959185</v>
+        <v>68.08430497959185</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1176268144047093</v>
+        <v>0.1184941115942521</v>
       </c>
       <c r="T33">
-        <v>1.476834903192855</v>
+        <v>1.494667446255965</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.147700899326725</v>
+        <v>7.893085246222762</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09358719588409144</v>
+        <v>0.09340728982893348</v>
       </c>
       <c r="C34">
-        <v>244.8974791008792</v>
+        <v>242.3625230149411</v>
       </c>
       <c r="D34">
-        <v>308.2974791008792</v>
+        <v>309.4625230149412</v>
       </c>
       <c r="E34">
-        <v>-35.59999999999999</v>
+        <v>-31.89999999999999</v>
       </c>
       <c r="F34">
-        <v>118.4</v>
+        <v>122.1</v>
       </c>
       <c r="G34">
         <v>55</v>
@@ -4075,28 +4075,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M34">
-        <v>6.3344</v>
+        <v>6.53235</v>
       </c>
       <c r="N34">
-        <v>43.66355918367347</v>
+        <v>43.46560918367347</v>
       </c>
       <c r="O34">
-        <v>10.47925420408163</v>
+        <v>10.43174620408163</v>
       </c>
       <c r="P34">
-        <v>33.18430497959184</v>
+        <v>33.03386297959184</v>
       </c>
       <c r="Q34">
-        <v>68.08430497959185</v>
+        <v>67.93386297959185</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1184941115942521</v>
+        <v>0.1193872982521395</v>
       </c>
       <c r="T34">
-        <v>1.494667446255965</v>
+        <v>1.513032304037376</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.893085246222762</v>
+        <v>7.653900844822074</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09340728982893348</v>
+        <v>0.09343410377377553</v>
       </c>
       <c r="C35">
-        <v>242.3625230149411</v>
+        <v>238.4883219622203</v>
       </c>
       <c r="D35">
-        <v>309.4625230149412</v>
+        <v>309.2883219622203</v>
       </c>
       <c r="E35">
-        <v>-31.89999999999999</v>
+        <v>-28.19999999999999</v>
       </c>
       <c r="F35">
-        <v>122.1</v>
+        <v>125.8</v>
       </c>
       <c r="G35">
         <v>55</v>
@@ -4157,45 +4157,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M35">
-        <v>6.53235</v>
+        <v>6.830940000000001</v>
       </c>
       <c r="N35">
-        <v>43.46560918367347</v>
+        <v>43.16701918367347</v>
       </c>
       <c r="O35">
-        <v>10.43174620408163</v>
+        <v>10.36008460408163</v>
       </c>
       <c r="P35">
-        <v>33.03386297959184</v>
+        <v>32.80693457959184</v>
       </c>
       <c r="Q35">
-        <v>67.93386297959185</v>
+        <v>67.70693457959185</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1193872982521395</v>
+        <v>0.1203075511723872</v>
       </c>
       <c r="T35">
-        <v>1.513032304037376</v>
+        <v>1.531953672660648</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.653900844822074</v>
+        <v>7.319338068212203</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09343410377377553</v>
+        <v>0.0932602777186176</v>
       </c>
       <c r="C36">
-        <v>238.4883219622203</v>
+        <v>235.9211086102854</v>
       </c>
       <c r="D36">
-        <v>309.2883219622203</v>
+        <v>310.4211086102854</v>
       </c>
       <c r="E36">
-        <v>-28.19999999999999</v>
+        <v>-24.5</v>
       </c>
       <c r="F36">
-        <v>125.8</v>
+        <v>129.5</v>
       </c>
       <c r="G36">
         <v>55</v>
@@ -4239,28 +4239,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M36">
-        <v>6.830940000000001</v>
+        <v>7.03185</v>
       </c>
       <c r="N36">
-        <v>43.16701918367347</v>
+        <v>42.96610918367347</v>
       </c>
       <c r="O36">
-        <v>10.36008460408163</v>
+        <v>10.31186620408163</v>
       </c>
       <c r="P36">
-        <v>32.80693457959184</v>
+        <v>32.65424297959184</v>
       </c>
       <c r="Q36">
-        <v>67.70693457959185</v>
+        <v>67.55424297959185</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1203075511723872</v>
+        <v>0.121256119567104</v>
       </c>
       <c r="T36">
-        <v>1.531953672660648</v>
+        <v>1.55145723724156</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.319338068212203</v>
+        <v>7.11021412340614</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0932602777186176</v>
+        <v>0.09308645166345965</v>
       </c>
       <c r="C37">
-        <v>235.9211086102854</v>
+        <v>233.3622235565181</v>
       </c>
       <c r="D37">
-        <v>310.4211086102854</v>
+        <v>311.5622235565181</v>
       </c>
       <c r="E37">
-        <v>-24.5</v>
+        <v>-20.79999999999998</v>
       </c>
       <c r="F37">
-        <v>129.5</v>
+        <v>133.2</v>
       </c>
       <c r="G37">
         <v>55</v>
@@ -4321,28 +4321,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M37">
-        <v>7.03185</v>
+        <v>7.232760000000001</v>
       </c>
       <c r="N37">
-        <v>42.96610918367347</v>
+        <v>42.76519918367347</v>
       </c>
       <c r="O37">
-        <v>10.31186620408163</v>
+        <v>10.26364780408163</v>
       </c>
       <c r="P37">
-        <v>32.65424297959184</v>
+        <v>32.50155137959184</v>
       </c>
       <c r="Q37">
-        <v>67.55424297959185</v>
+        <v>67.40155137959184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.121256119567104</v>
+        <v>0.1222343307241557</v>
       </c>
       <c r="T37">
-        <v>1.55145723724156</v>
+        <v>1.571570288215625</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.11021412340614</v>
+        <v>6.912708175533748</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09308645166345964</v>
+        <v>0.09291262560830169</v>
       </c>
       <c r="C38">
-        <v>233.3622235565182</v>
+        <v>230.8117589848202</v>
       </c>
       <c r="D38">
-        <v>311.5622235565182</v>
+        <v>312.7117589848202</v>
       </c>
       <c r="E38">
-        <v>-20.80000000000001</v>
+        <v>-17.09999999999999</v>
       </c>
       <c r="F38">
-        <v>133.2</v>
+        <v>136.9</v>
       </c>
       <c r="G38">
         <v>55</v>
@@ -4403,28 +4403,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M38">
-        <v>7.23276</v>
+        <v>7.43367</v>
       </c>
       <c r="N38">
-        <v>42.76519918367347</v>
+        <v>42.56428918367347</v>
       </c>
       <c r="O38">
-        <v>10.26364780408163</v>
+        <v>10.21542940408163</v>
       </c>
       <c r="P38">
-        <v>32.50155137959184</v>
+        <v>32.34885977959184</v>
       </c>
       <c r="Q38">
-        <v>67.40155137959184</v>
+        <v>67.24885977959184</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1222343307241557</v>
+        <v>0.1232435962036535</v>
       </c>
       <c r="T38">
-        <v>1.571570288215625</v>
+        <v>1.592321848744422</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.912708175533749</v>
+        <v>6.725878224843647</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09291262560830169</v>
+        <v>0.09273879955314374</v>
       </c>
       <c r="C39">
-        <v>230.8117589848202</v>
+        <v>228.2698084446128</v>
       </c>
       <c r="D39">
-        <v>312.7117589848202</v>
+        <v>313.8698084446128</v>
       </c>
       <c r="E39">
-        <v>-17.09999999999999</v>
+        <v>-13.40000000000001</v>
       </c>
       <c r="F39">
-        <v>136.9</v>
+        <v>140.6</v>
       </c>
       <c r="G39">
         <v>55</v>
@@ -4485,28 +4485,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M39">
-        <v>7.43367</v>
+        <v>7.63458</v>
       </c>
       <c r="N39">
-        <v>42.56428918367347</v>
+        <v>42.36337918367347</v>
       </c>
       <c r="O39">
-        <v>10.21542940408163</v>
+        <v>10.16721100408163</v>
       </c>
       <c r="P39">
-        <v>32.34885977959184</v>
+        <v>32.19616817959184</v>
       </c>
       <c r="Q39">
-        <v>67.24885977959184</v>
+        <v>67.09616817959184</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1232435962036535</v>
+        <v>0.1242854186341028</v>
       </c>
       <c r="T39">
-        <v>1.592321848744422</v>
+        <v>1.613742814451567</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.725878224843647</v>
+        <v>6.548881429453025</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09273879955314374</v>
+        <v>0.09256497349798579</v>
       </c>
       <c r="C40">
-        <v>228.2698084446128</v>
+        <v>225.7364668762157</v>
       </c>
       <c r="D40">
-        <v>313.8698084446128</v>
+        <v>315.0364668762157</v>
       </c>
       <c r="E40">
-        <v>-13.40000000000001</v>
+        <v>-9.699999999999989</v>
       </c>
       <c r="F40">
-        <v>140.6</v>
+        <v>144.3</v>
       </c>
       <c r="G40">
         <v>55</v>
@@ -4567,28 +4567,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M40">
-        <v>7.63458</v>
+        <v>7.835490000000001</v>
       </c>
       <c r="N40">
-        <v>42.36337918367347</v>
+        <v>42.16246918367347</v>
       </c>
       <c r="O40">
-        <v>10.16721100408163</v>
+        <v>10.11899260408163</v>
       </c>
       <c r="P40">
-        <v>32.19616817959184</v>
+        <v>32.04347657959184</v>
       </c>
       <c r="Q40">
-        <v>67.09616817959184</v>
+        <v>66.94347657959185</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1242854186341028</v>
+        <v>0.1253613991770259</v>
       </c>
       <c r="T40">
-        <v>1.613742814451567</v>
+        <v>1.635866106903209</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.548881429453025</v>
+        <v>6.380961392800383</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09256497349798579</v>
+        <v>0.09239114744282785</v>
       </c>
       <c r="C41">
-        <v>225.7364668762157</v>
+        <v>223.2118306367924</v>
       </c>
       <c r="D41">
-        <v>315.0364668762157</v>
+        <v>316.2118306367924</v>
       </c>
       <c r="E41">
-        <v>-9.699999999999989</v>
+        <v>-6</v>
       </c>
       <c r="F41">
-        <v>144.3</v>
+        <v>148</v>
       </c>
       <c r="G41">
         <v>55</v>
@@ -4649,28 +4649,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M41">
-        <v>7.835490000000001</v>
+        <v>8.0364</v>
       </c>
       <c r="N41">
-        <v>42.16246918367347</v>
+        <v>41.96155918367347</v>
       </c>
       <c r="O41">
-        <v>10.11899260408163</v>
+        <v>10.07077420408163</v>
       </c>
       <c r="P41">
-        <v>32.04347657959184</v>
+        <v>31.89078497959184</v>
       </c>
       <c r="Q41">
-        <v>66.94347657959185</v>
+        <v>66.79078497959185</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1253613991770259</v>
+        <v>0.1264732457380464</v>
       </c>
       <c r="T41">
-        <v>1.635866106903209</v>
+        <v>1.658726842436573</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.380961392800383</v>
+        <v>6.221437357980373</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09239114744282785</v>
+        <v>0.0925289213876699</v>
       </c>
       <c r="C42">
-        <v>223.2118306367924</v>
+        <v>218.579522549663</v>
       </c>
       <c r="D42">
-        <v>316.2118306367924</v>
+        <v>315.2795225496631</v>
       </c>
       <c r="E42">
-        <v>-6</v>
+        <v>-2.299999999999983</v>
       </c>
       <c r="F42">
-        <v>148</v>
+        <v>151.7</v>
       </c>
       <c r="G42">
         <v>55</v>
@@ -4731,45 +4731,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M42">
-        <v>8.0364</v>
+        <v>8.389010000000001</v>
       </c>
       <c r="N42">
-        <v>41.96155918367347</v>
+        <v>41.60894918367347</v>
       </c>
       <c r="O42">
-        <v>10.07077420408163</v>
+        <v>9.986147804081634</v>
       </c>
       <c r="P42">
-        <v>31.89078497959184</v>
+        <v>31.62280137959184</v>
       </c>
       <c r="Q42">
-        <v>66.79078497959185</v>
+        <v>66.52280137959184</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1264732457380464</v>
+        <v>0.1276227820129998</v>
       </c>
       <c r="T42">
-        <v>1.658726842436573</v>
+        <v>1.682362518157508</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.221437357980373</v>
+        <v>5.959935580440775</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0925289213876699</v>
+        <v>0.09236269533251194</v>
       </c>
       <c r="C43">
-        <v>218.579522549663</v>
+        <v>216.0050517083868</v>
       </c>
       <c r="D43">
-        <v>315.2795225496631</v>
+        <v>316.4050517083868</v>
       </c>
       <c r="E43">
-        <v>-2.299999999999983</v>
+        <v>1.400000000000006</v>
       </c>
       <c r="F43">
-        <v>151.7</v>
+        <v>155.4</v>
       </c>
       <c r="G43">
         <v>55</v>
@@ -4813,28 +4813,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M43">
-        <v>8.389010000000001</v>
+        <v>8.593620000000001</v>
       </c>
       <c r="N43">
-        <v>41.60894918367347</v>
+        <v>41.40433918367347</v>
       </c>
       <c r="O43">
-        <v>9.986147804081634</v>
+        <v>9.937041404081633</v>
       </c>
       <c r="P43">
-        <v>31.62280137959184</v>
+        <v>31.46729777959184</v>
       </c>
       <c r="Q43">
-        <v>66.52280137959184</v>
+        <v>66.36729777959184</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1276227820129998</v>
+        <v>0.1288119574698482</v>
       </c>
       <c r="T43">
-        <v>1.682362518157508</v>
+        <v>1.706813217179165</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.959935580440775</v>
+        <v>5.818032352335043</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09236269533251194</v>
+        <v>0.09219646927735399</v>
       </c>
       <c r="C44">
-        <v>216.0050517083868</v>
+        <v>213.4386458028668</v>
       </c>
       <c r="D44">
-        <v>316.4050517083868</v>
+        <v>317.5386458028668</v>
       </c>
       <c r="E44">
-        <v>1.400000000000006</v>
+        <v>5.099999999999994</v>
       </c>
       <c r="F44">
-        <v>155.4</v>
+        <v>159.1</v>
       </c>
       <c r="G44">
         <v>55</v>
@@ -4895,28 +4895,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M44">
-        <v>8.593620000000001</v>
+        <v>8.79823</v>
       </c>
       <c r="N44">
-        <v>41.40433918367347</v>
+        <v>41.19972918367347</v>
       </c>
       <c r="O44">
-        <v>9.937041404081633</v>
+        <v>9.887935004081632</v>
       </c>
       <c r="P44">
-        <v>31.46729777959184</v>
+        <v>31.31179417959184</v>
       </c>
       <c r="Q44">
-        <v>66.36729777959184</v>
+        <v>66.21179417959183</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1288119574698482</v>
+        <v>0.1300428583813228</v>
       </c>
       <c r="T44">
-        <v>1.706813217179165</v>
+        <v>1.73212183546474</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.818032352335043</v>
+        <v>5.682729274373762</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09219646927735399</v>
+        <v>0.09203024322219606</v>
       </c>
       <c r="C45">
-        <v>213.4386458028668</v>
+        <v>210.8803918282622</v>
       </c>
       <c r="D45">
-        <v>317.5386458028668</v>
+        <v>318.6803918282622</v>
       </c>
       <c r="E45">
-        <v>5.099999999999994</v>
+        <v>8.800000000000011</v>
       </c>
       <c r="F45">
-        <v>159.1</v>
+        <v>162.8</v>
       </c>
       <c r="G45">
         <v>55</v>
@@ -4977,28 +4977,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M45">
-        <v>8.79823</v>
+        <v>9.002840000000001</v>
       </c>
       <c r="N45">
-        <v>41.19972918367347</v>
+        <v>40.99511918367347</v>
       </c>
       <c r="O45">
-        <v>9.887935004081632</v>
+        <v>9.838828604081634</v>
       </c>
       <c r="P45">
-        <v>31.31179417959184</v>
+        <v>31.15629057959184</v>
       </c>
       <c r="Q45">
-        <v>66.21179417959183</v>
+        <v>66.05629057959185</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1300428583813228</v>
+        <v>0.1313177200396358</v>
       </c>
       <c r="T45">
-        <v>1.73212183546474</v>
+        <v>1.758334332974799</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.682729274373762</v>
+        <v>5.553576336319813</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09203024322219606</v>
+        <v>0.0918640171670381</v>
       </c>
       <c r="C46">
-        <v>210.8803918282622</v>
+        <v>208.330378035451</v>
       </c>
       <c r="D46">
-        <v>318.6803918282622</v>
+        <v>319.830378035451</v>
       </c>
       <c r="E46">
-        <v>8.800000000000011</v>
+        <v>12.5</v>
       </c>
       <c r="F46">
-        <v>162.8</v>
+        <v>166.5</v>
       </c>
       <c r="G46">
         <v>55</v>
@@ -5059,28 +5059,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M46">
-        <v>9.002840000000001</v>
+        <v>9.20745</v>
       </c>
       <c r="N46">
-        <v>40.99511918367347</v>
+        <v>40.79050918367347</v>
       </c>
       <c r="O46">
-        <v>9.838828604081634</v>
+        <v>9.789722204081633</v>
       </c>
       <c r="P46">
-        <v>31.15629057959184</v>
+        <v>31.00078697959184</v>
       </c>
       <c r="Q46">
-        <v>66.05629057959185</v>
+        <v>65.90078697959184</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1313177200396358</v>
+        <v>0.1326389403037056</v>
       </c>
       <c r="T46">
-        <v>1.758334332974799</v>
+        <v>1.785500012212498</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.553576336319813</v>
+        <v>5.43016352884604</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0918640171670381</v>
+        <v>0.09169779111188014</v>
       </c>
       <c r="C47">
-        <v>208.330378035451</v>
+        <v>205.7886939537687</v>
       </c>
       <c r="D47">
-        <v>319.830378035451</v>
+        <v>320.9886939537687</v>
       </c>
       <c r="E47">
-        <v>12.5</v>
+        <v>16.20000000000002</v>
       </c>
       <c r="F47">
-        <v>166.5</v>
+        <v>170.2</v>
       </c>
       <c r="G47">
         <v>55</v>
@@ -5141,28 +5141,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M47">
-        <v>9.20745</v>
+        <v>9.412060000000002</v>
       </c>
       <c r="N47">
-        <v>40.79050918367347</v>
+        <v>40.58589918367347</v>
       </c>
       <c r="O47">
-        <v>9.789722204081633</v>
+        <v>9.740615804081632</v>
       </c>
       <c r="P47">
-        <v>31.00078697959184</v>
+        <v>30.84528337959184</v>
       </c>
       <c r="Q47">
-        <v>65.90078697959184</v>
+        <v>65.74528337959184</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1326389403037056</v>
+        <v>0.1340090946516299</v>
       </c>
       <c r="T47">
-        <v>1.785500012212498</v>
+        <v>1.813671827718259</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.43016352884604</v>
+        <v>5.312116495610256</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09169779111188014</v>
+        <v>0.09153156505672221</v>
       </c>
       <c r="C48">
-        <v>205.7886939537687</v>
+        <v>203.2554304142431</v>
       </c>
       <c r="D48">
-        <v>320.9886939537687</v>
+        <v>322.1554304142431</v>
       </c>
       <c r="E48">
-        <v>16.20000000000002</v>
+        <v>19.90000000000001</v>
       </c>
       <c r="F48">
-        <v>170.2</v>
+        <v>173.9</v>
       </c>
       <c r="G48">
         <v>55</v>
@@ -5223,28 +5223,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M48">
-        <v>9.412060000000002</v>
+        <v>9.616670000000001</v>
       </c>
       <c r="N48">
-        <v>40.58589918367347</v>
+        <v>40.38128918367347</v>
       </c>
       <c r="O48">
-        <v>9.740615804081632</v>
+        <v>9.691509404081634</v>
       </c>
       <c r="P48">
-        <v>30.84528337959184</v>
+        <v>30.68977977959184</v>
       </c>
       <c r="Q48">
-        <v>65.74528337959184</v>
+        <v>65.58977977959185</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1340090946516299</v>
+        <v>0.1354309529372117</v>
       </c>
       <c r="T48">
-        <v>1.813671827718259</v>
+        <v>1.842906730601596</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.312116495610256</v>
+        <v>5.199092740384506</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09153156505672221</v>
+        <v>0.09136533900156424</v>
       </c>
       <c r="C49">
-        <v>203.2554304142431</v>
+        <v>200.7306795733383</v>
       </c>
       <c r="D49">
-        <v>322.1554304142431</v>
+        <v>323.3306795733383</v>
       </c>
       <c r="E49">
-        <v>19.90000000000001</v>
+        <v>23.60000000000002</v>
       </c>
       <c r="F49">
-        <v>173.9</v>
+        <v>177.6</v>
       </c>
       <c r="G49">
         <v>55</v>
@@ -5305,28 +5305,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M49">
-        <v>9.616670000000001</v>
+        <v>9.821280000000002</v>
       </c>
       <c r="N49">
-        <v>40.38128918367347</v>
+        <v>40.17667918367347</v>
       </c>
       <c r="O49">
-        <v>9.691509404081634</v>
+        <v>9.642403004081633</v>
       </c>
       <c r="P49">
-        <v>30.68977977959184</v>
+        <v>30.53427617959184</v>
       </c>
       <c r="Q49">
-        <v>65.58977977959185</v>
+        <v>65.43427617959185</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1354309529372117</v>
+        <v>0.1369074980799312</v>
       </c>
       <c r="T49">
-        <v>1.842906730601596</v>
+        <v>1.873266052826599</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.199092740384506</v>
+        <v>5.090778308293162</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09136533900156424</v>
+        <v>0.09119911294640629</v>
       </c>
       <c r="C50">
-        <v>200.7306795733383</v>
+        <v>198.2145349372188</v>
       </c>
       <c r="D50">
-        <v>323.3306795733383</v>
+        <v>324.5145349372187</v>
       </c>
       <c r="E50">
-        <v>23.59999999999999</v>
+        <v>27.29999999999998</v>
       </c>
       <c r="F50">
-        <v>177.6</v>
+        <v>181.3</v>
       </c>
       <c r="G50">
         <v>55</v>
@@ -5387,28 +5387,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M50">
-        <v>9.82128</v>
+        <v>10.02589</v>
       </c>
       <c r="N50">
-        <v>40.17667918367347</v>
+        <v>39.97206918367348</v>
       </c>
       <c r="O50">
-        <v>9.642403004081633</v>
+        <v>9.593296604081633</v>
       </c>
       <c r="P50">
-        <v>30.53427617959184</v>
+        <v>30.37877257959184</v>
       </c>
       <c r="Q50">
-        <v>65.43427617959185</v>
+        <v>65.27877257959184</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1369074980799312</v>
+        <v>0.1384419469537378</v>
       </c>
       <c r="T50">
-        <v>1.873266052826599</v>
+        <v>1.904815936707486</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.090778308293163</v>
+        <v>4.986884873430038</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09119911294640629</v>
+        <v>0.09103288689124835</v>
       </c>
       <c r="C51">
-        <v>198.2145349372188</v>
+        <v>195.70709138655</v>
       </c>
       <c r="D51">
-        <v>324.5145349372187</v>
+        <v>325.70709138655</v>
       </c>
       <c r="E51">
-        <v>27.29999999999998</v>
+        <v>31</v>
       </c>
       <c r="F51">
-        <v>181.3</v>
+        <v>185</v>
       </c>
       <c r="G51">
         <v>55</v>
@@ -5469,28 +5469,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M51">
-        <v>10.02589</v>
+        <v>10.2305</v>
       </c>
       <c r="N51">
-        <v>39.97206918367348</v>
+        <v>39.76745918367347</v>
       </c>
       <c r="O51">
-        <v>9.593296604081633</v>
+        <v>9.544190204081634</v>
       </c>
       <c r="P51">
-        <v>30.37877257959184</v>
+        <v>30.22326897959184</v>
       </c>
       <c r="Q51">
-        <v>65.27877257959184</v>
+        <v>65.12326897959184</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1384419469537378</v>
+        <v>0.1400377737824967</v>
       </c>
       <c r="T51">
-        <v>1.904815936707486</v>
+        <v>1.937627815943607</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.986884873430038</v>
+        <v>4.887147175961436</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09103288689124835</v>
+        <v>0.09086666083609039</v>
       </c>
       <c r="C52">
-        <v>195.70709138655</v>
+        <v>193.2084452018475</v>
       </c>
       <c r="D52">
-        <v>325.70709138655</v>
+        <v>326.9084452018475</v>
       </c>
       <c r="E52">
-        <v>31</v>
+        <v>34.70000000000002</v>
       </c>
       <c r="F52">
-        <v>185</v>
+        <v>188.7</v>
       </c>
       <c r="G52">
         <v>55</v>
@@ -5551,28 +5551,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M52">
-        <v>10.2305</v>
+        <v>10.43511</v>
       </c>
       <c r="N52">
-        <v>39.76745918367347</v>
+        <v>39.56284918367347</v>
       </c>
       <c r="O52">
-        <v>9.544190204081634</v>
+        <v>9.495083804081633</v>
       </c>
       <c r="P52">
-        <v>30.22326897959184</v>
+        <v>30.06776537959184</v>
       </c>
       <c r="Q52">
-        <v>65.12326897959184</v>
+        <v>64.96776537959184</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1400377737824967</v>
+        <v>0.1416987364001845</v>
       </c>
       <c r="T52">
-        <v>1.937627815943607</v>
+        <v>1.971778955556714</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.887147175961436</v>
+        <v>4.791320760746505</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09086666083609039</v>
+        <v>0.09070043478093245</v>
       </c>
       <c r="C53">
-        <v>193.2084452018475</v>
+        <v>190.7186940893882</v>
       </c>
       <c r="D53">
-        <v>326.9084452018475</v>
+        <v>328.1186940893882</v>
       </c>
       <c r="E53">
-        <v>34.70000000000002</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="F53">
-        <v>188.7</v>
+        <v>192.4</v>
       </c>
       <c r="G53">
         <v>55</v>
@@ -5633,28 +5633,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M53">
-        <v>10.43511</v>
+        <v>10.63972</v>
       </c>
       <c r="N53">
-        <v>39.56284918367347</v>
+        <v>39.35823918367348</v>
       </c>
       <c r="O53">
-        <v>9.495083804081633</v>
+        <v>9.445977404081633</v>
       </c>
       <c r="P53">
-        <v>30.06776537959184</v>
+        <v>29.91226177959184</v>
       </c>
       <c r="Q53">
-        <v>64.96776537959184</v>
+        <v>64.81226177959185</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1416987364001845</v>
+        <v>0.1434289057936093</v>
       </c>
       <c r="T53">
-        <v>1.971778955556714</v>
+        <v>2.007353059320366</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.791320760746505</v>
+        <v>4.699179976885997</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09070043478093245</v>
+        <v>0.0905342087257745</v>
       </c>
       <c r="C54">
-        <v>190.7186940893882</v>
+        <v>188.2379372077008</v>
       </c>
       <c r="D54">
-        <v>328.1186940893882</v>
+        <v>329.3379372077008</v>
       </c>
       <c r="E54">
-        <v>38.40000000000001</v>
+        <v>42.10000000000002</v>
       </c>
       <c r="F54">
-        <v>192.4</v>
+        <v>196.1</v>
       </c>
       <c r="G54">
         <v>55</v>
@@ -5715,28 +5715,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M54">
-        <v>10.63972</v>
+        <v>10.84433</v>
       </c>
       <c r="N54">
-        <v>39.35823918367348</v>
+        <v>39.15362918367347</v>
       </c>
       <c r="O54">
-        <v>9.445977404081633</v>
+        <v>9.396871004081634</v>
       </c>
       <c r="P54">
-        <v>29.91226177959184</v>
+        <v>29.75675817959184</v>
       </c>
       <c r="Q54">
-        <v>64.81226177959185</v>
+        <v>64.65675817959185</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1434289057936093</v>
+        <v>0.1452326994165415</v>
       </c>
       <c r="T54">
-        <v>2.007353059320366</v>
+        <v>2.044440954733536</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.699179976885997</v>
+        <v>4.610516203737204</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0905342087257745</v>
+        <v>0.09036798267061653</v>
       </c>
       <c r="C55">
-        <v>188.2379372077008</v>
+        <v>185.7662751946474</v>
       </c>
       <c r="D55">
-        <v>329.3379372077008</v>
+        <v>330.5662751946475</v>
       </c>
       <c r="E55">
-        <v>42.10000000000002</v>
+        <v>45.80000000000001</v>
       </c>
       <c r="F55">
-        <v>196.1</v>
+        <v>199.8</v>
       </c>
       <c r="G55">
         <v>55</v>
@@ -5797,28 +5797,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M55">
-        <v>10.84433</v>
+        <v>11.04894</v>
       </c>
       <c r="N55">
-        <v>39.15362918367347</v>
+        <v>38.94901918367347</v>
       </c>
       <c r="O55">
-        <v>9.396871004081634</v>
+        <v>9.347764604081632</v>
       </c>
       <c r="P55">
-        <v>29.75675817959184</v>
+        <v>29.60125457959184</v>
       </c>
       <c r="Q55">
-        <v>64.65675817959185</v>
+        <v>64.50125457959184</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1452326994165415</v>
+        <v>0.1471149188491664</v>
       </c>
       <c r="T55">
-        <v>2.044440954733536</v>
+        <v>2.083141367338582</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.610516203737204</v>
+        <v>4.525136274038366</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09036798267061653</v>
+        <v>0.09124675661545859</v>
       </c>
       <c r="C56">
-        <v>185.7662751946474</v>
+        <v>175.6743332538284</v>
       </c>
       <c r="D56">
-        <v>330.5662751946475</v>
+        <v>324.1743332538284</v>
       </c>
       <c r="E56">
-        <v>45.80000000000001</v>
+        <v>49.50000000000003</v>
       </c>
       <c r="F56">
-        <v>199.8</v>
+        <v>203.5</v>
       </c>
       <c r="G56">
         <v>55</v>
@@ -5879,45 +5879,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M56">
-        <v>11.04894</v>
+        <v>11.7623</v>
       </c>
       <c r="N56">
-        <v>38.94901918367347</v>
+        <v>38.23565918367347</v>
       </c>
       <c r="O56">
-        <v>9.347764604081632</v>
+        <v>9.176558204081632</v>
       </c>
       <c r="P56">
-        <v>29.60125457959184</v>
+        <v>29.05910097959184</v>
       </c>
       <c r="Q56">
-        <v>64.50125457959184</v>
+        <v>63.95910097959185</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1471149188491664</v>
+        <v>0.1490807924787969</v>
       </c>
       <c r="T56">
-        <v>2.083141367338582</v>
+        <v>2.123561798281631</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.24</v>
       </c>
       <c r="W56">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.525136274038366</v>
+        <v>4.250695797902916</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09124675661545859</v>
+        <v>0.09109953056030062</v>
       </c>
       <c r="C57">
-        <v>175.6743332538284</v>
+        <v>173.0279183059934</v>
       </c>
       <c r="D57">
-        <v>324.1743332538284</v>
+        <v>325.2279183059934</v>
       </c>
       <c r="E57">
-        <v>49.50000000000003</v>
+        <v>53.20000000000002</v>
       </c>
       <c r="F57">
-        <v>203.5</v>
+        <v>207.2</v>
       </c>
       <c r="G57">
         <v>55</v>
@@ -5961,28 +5961,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M57">
-        <v>11.7623</v>
+        <v>11.97616</v>
       </c>
       <c r="N57">
-        <v>38.23565918367347</v>
+        <v>38.02179918367347</v>
       </c>
       <c r="O57">
-        <v>9.176558204081632</v>
+        <v>9.125231804081633</v>
       </c>
       <c r="P57">
-        <v>29.05910097959184</v>
+        <v>28.89656737959184</v>
       </c>
       <c r="Q57">
-        <v>63.95910097959185</v>
+        <v>63.79656737959185</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1490807924787969</v>
+        <v>0.1511360240006833</v>
       </c>
       <c r="T57">
-        <v>2.123561798281631</v>
+        <v>2.165819521540272</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.250695797902916</v>
+        <v>4.174790515797507</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09109953056030062</v>
+        <v>0.09095230450514269</v>
       </c>
       <c r="C58">
-        <v>173.0279183059934</v>
+        <v>170.3883741113878</v>
       </c>
       <c r="D58">
-        <v>325.2279183059934</v>
+        <v>326.2883741113878</v>
       </c>
       <c r="E58">
-        <v>53.20000000000002</v>
+        <v>56.90000000000003</v>
       </c>
       <c r="F58">
-        <v>207.2</v>
+        <v>210.9</v>
       </c>
       <c r="G58">
         <v>55</v>
@@ -6043,28 +6043,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M58">
-        <v>11.97616</v>
+        <v>12.19002</v>
       </c>
       <c r="N58">
-        <v>38.02179918367347</v>
+        <v>37.80793918367347</v>
       </c>
       <c r="O58">
-        <v>9.125231804081633</v>
+        <v>9.073905404081632</v>
       </c>
       <c r="P58">
-        <v>28.89656737959184</v>
+        <v>28.73403377959184</v>
       </c>
       <c r="Q58">
-        <v>63.79656737959185</v>
+        <v>63.63403377959185</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1511360240006833</v>
+        <v>0.1532868476863784</v>
       </c>
       <c r="T58">
-        <v>2.165819521540272</v>
+        <v>2.210042720299316</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.174790515797507</v>
+        <v>4.101548576923866</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09095230450514269</v>
+        <v>0.09080507844998473</v>
       </c>
       <c r="C59">
-        <v>170.3883741113878</v>
+        <v>167.7557680993288</v>
       </c>
       <c r="D59">
-        <v>326.2883741113878</v>
+        <v>327.3557680993288</v>
       </c>
       <c r="E59">
-        <v>56.90000000000003</v>
+        <v>60.60000000000002</v>
       </c>
       <c r="F59">
-        <v>210.9</v>
+        <v>214.6</v>
       </c>
       <c r="G59">
         <v>55</v>
@@ -6125,28 +6125,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M59">
-        <v>12.19002</v>
+        <v>12.40388</v>
       </c>
       <c r="N59">
-        <v>37.80793918367347</v>
+        <v>37.59407918367347</v>
       </c>
       <c r="O59">
-        <v>9.073905404081632</v>
+        <v>9.022579004081633</v>
       </c>
       <c r="P59">
-        <v>28.73403377959184</v>
+        <v>28.57150017959184</v>
       </c>
       <c r="Q59">
-        <v>63.63403377959185</v>
+        <v>63.47150017959184</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1532868476863784</v>
+        <v>0.1555400915475827</v>
       </c>
       <c r="T59">
-        <v>2.210042720299316</v>
+        <v>2.256371785665932</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.101548576923866</v>
+        <v>4.030832222149316</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09080507844998474</v>
+        <v>0.09222725239482681</v>
       </c>
       <c r="C60">
-        <v>167.7557680993288</v>
+        <v>154.0281050335622</v>
       </c>
       <c r="D60">
-        <v>327.3557680993288</v>
+        <v>317.3281050335622</v>
       </c>
       <c r="E60">
-        <v>60.59999999999999</v>
+        <v>64.29999999999998</v>
       </c>
       <c r="F60">
-        <v>214.6</v>
+        <v>218.3</v>
       </c>
       <c r="G60">
         <v>55</v>
@@ -6207,45 +6207,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M60">
-        <v>12.40388</v>
+        <v>13.38179</v>
       </c>
       <c r="N60">
-        <v>37.59407918367347</v>
+        <v>36.61616918367348</v>
       </c>
       <c r="O60">
-        <v>9.022579004081633</v>
+        <v>8.787880604081634</v>
       </c>
       <c r="P60">
-        <v>28.57150017959184</v>
+        <v>27.82828857959184</v>
       </c>
       <c r="Q60">
-        <v>63.47150017959184</v>
+        <v>62.72828857959185</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1555400915475827</v>
+        <v>0.15790324974348</v>
       </c>
       <c r="T60">
-        <v>2.256371785665932</v>
+        <v>2.304960805440677</v>
       </c>
       <c r="U60">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.030832222149317</v>
+        <v>3.736268405323464</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09222725239482681</v>
+        <v>0.09210662633966885</v>
       </c>
       <c r="C61">
-        <v>154.0281050335622</v>
+        <v>151.1547262004805</v>
       </c>
       <c r="D61">
-        <v>317.3281050335622</v>
+        <v>318.1547262004805</v>
       </c>
       <c r="E61">
-        <v>64.29999999999998</v>
+        <v>68</v>
       </c>
       <c r="F61">
-        <v>218.3</v>
+        <v>222</v>
       </c>
       <c r="G61">
         <v>55</v>
@@ -6289,28 +6289,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M61">
-        <v>13.38179</v>
+        <v>13.6086</v>
       </c>
       <c r="N61">
-        <v>36.61616918367348</v>
+        <v>36.38935918367347</v>
       </c>
       <c r="O61">
-        <v>8.787880604081634</v>
+        <v>8.733446204081632</v>
       </c>
       <c r="P61">
-        <v>27.82828857959184</v>
+        <v>27.65591297959184</v>
       </c>
       <c r="Q61">
-        <v>62.72828857959185</v>
+        <v>62.55591297959185</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.15790324974348</v>
+        <v>0.1603845658491721</v>
       </c>
       <c r="T61">
-        <v>2.304960805440677</v>
+        <v>2.355979276204159</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.736268405323464</v>
+        <v>3.673997265234739</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09210662633966885</v>
+        <v>0.0919860002845109</v>
       </c>
       <c r="C62">
-        <v>151.1547262004805</v>
+        <v>148.2856652147925</v>
       </c>
       <c r="D62">
-        <v>318.1547262004805</v>
+        <v>318.9856652147924</v>
       </c>
       <c r="E62">
-        <v>68</v>
+        <v>71.69999999999999</v>
       </c>
       <c r="F62">
-        <v>222</v>
+        <v>225.7</v>
       </c>
       <c r="G62">
         <v>55</v>
@@ -6371,28 +6371,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M62">
-        <v>13.6086</v>
+        <v>13.83541</v>
       </c>
       <c r="N62">
-        <v>36.38935918367347</v>
+        <v>36.16254918367348</v>
       </c>
       <c r="O62">
-        <v>8.733446204081632</v>
+        <v>8.679011804081634</v>
       </c>
       <c r="P62">
-        <v>27.65591297959184</v>
+        <v>27.48353737959184</v>
       </c>
       <c r="Q62">
-        <v>62.55591297959185</v>
+        <v>62.38353737959185</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1603845658491721</v>
+        <v>0.1629931289346433</v>
       </c>
       <c r="T62">
-        <v>2.355979276204159</v>
+        <v>2.409614078801666</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.673997265234739</v>
+        <v>3.613767801870236</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0919860002845109</v>
+        <v>0.09186537422935295</v>
       </c>
       <c r="C63">
-        <v>148.2856652147925</v>
+        <v>145.4209559964372</v>
       </c>
       <c r="D63">
-        <v>318.9856652147924</v>
+        <v>319.8209559964372</v>
       </c>
       <c r="E63">
-        <v>71.69999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F63">
-        <v>225.7</v>
+        <v>229.4</v>
       </c>
       <c r="G63">
         <v>55</v>
@@ -6453,28 +6453,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M63">
-        <v>13.83541</v>
+        <v>14.06222</v>
       </c>
       <c r="N63">
-        <v>36.16254918367348</v>
+        <v>35.93573918367348</v>
       </c>
       <c r="O63">
-        <v>8.679011804081634</v>
+        <v>8.624577404081634</v>
       </c>
       <c r="P63">
-        <v>27.48353737959184</v>
+        <v>27.31116177959184</v>
       </c>
       <c r="Q63">
-        <v>62.38353737959185</v>
+        <v>62.21116177959185</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1629931289346433</v>
+        <v>0.1657389848140867</v>
       </c>
       <c r="T63">
-        <v>2.409614078801666</v>
+        <v>2.46607176574641</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.613767801870236</v>
+        <v>3.555481224420716</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09186537422935295</v>
+        <v>0.09308538817419498</v>
       </c>
       <c r="C64">
-        <v>145.4209559964372</v>
+        <v>133.4692308603137</v>
       </c>
       <c r="D64">
-        <v>319.8209559964372</v>
+        <v>311.5692308603137</v>
       </c>
       <c r="E64">
-        <v>75.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F64">
-        <v>229.4</v>
+        <v>233.1</v>
       </c>
       <c r="G64">
         <v>55</v>
@@ -6535,45 +6535,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M64">
-        <v>14.06222</v>
+        <v>14.94171</v>
       </c>
       <c r="N64">
-        <v>35.93573918367348</v>
+        <v>35.05624918367347</v>
       </c>
       <c r="O64">
-        <v>8.624577404081634</v>
+        <v>8.413499804081633</v>
       </c>
       <c r="P64">
-        <v>27.31116177959184</v>
+        <v>26.64274937959184</v>
       </c>
       <c r="Q64">
-        <v>62.21116177959185</v>
+        <v>61.54274937959185</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1657389848140867</v>
+        <v>0.1686332653356621</v>
       </c>
       <c r="T64">
-        <v>2.46607176574641</v>
+        <v>2.525581219553031</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.555481224420716</v>
+        <v>3.34620061449951</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09308538817419498</v>
+        <v>0.09298604211903704</v>
       </c>
       <c r="C65">
-        <v>133.4692308603137</v>
+        <v>130.4252124303823</v>
       </c>
       <c r="D65">
-        <v>311.5692308603137</v>
+        <v>312.2252124303823</v>
       </c>
       <c r="E65">
-        <v>79.09999999999999</v>
+        <v>82.80000000000001</v>
       </c>
       <c r="F65">
-        <v>233.1</v>
+        <v>236.8</v>
       </c>
       <c r="G65">
         <v>55</v>
@@ -6617,28 +6617,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M65">
-        <v>14.94171</v>
+        <v>15.17888</v>
       </c>
       <c r="N65">
-        <v>35.05624918367347</v>
+        <v>34.81907918367347</v>
       </c>
       <c r="O65">
-        <v>8.413499804081633</v>
+        <v>8.356579004081633</v>
       </c>
       <c r="P65">
-        <v>26.64274937959184</v>
+        <v>26.46250017959184</v>
       </c>
       <c r="Q65">
-        <v>61.54274937959185</v>
+        <v>61.36250017959185</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1686332653356621</v>
+        <v>0.1716883392195473</v>
       </c>
       <c r="T65">
-        <v>2.525581219553031</v>
+        <v>2.588396754126687</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.34620061449951</v>
+        <v>3.293916229897955</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09298604211903704</v>
+        <v>0.0928866960638791</v>
       </c>
       <c r="C66">
-        <v>130.4252124303823</v>
+        <v>127.383962051161</v>
       </c>
       <c r="D66">
-        <v>312.2252124303823</v>
+        <v>312.883962051161</v>
       </c>
       <c r="E66">
-        <v>82.80000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="F66">
-        <v>236.8</v>
+        <v>240.5</v>
       </c>
       <c r="G66">
         <v>55</v>
@@ -6699,28 +6699,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M66">
-        <v>15.17888</v>
+        <v>15.41605</v>
       </c>
       <c r="N66">
-        <v>34.81907918367347</v>
+        <v>34.58190918367347</v>
       </c>
       <c r="O66">
-        <v>8.356579004081633</v>
+        <v>8.299658204081634</v>
       </c>
       <c r="P66">
-        <v>26.46250017959184</v>
+        <v>26.28225097959184</v>
       </c>
       <c r="Q66">
-        <v>61.36250017959185</v>
+        <v>61.18225097959184</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1716883392195473</v>
+        <v>0.1749179887539403</v>
       </c>
       <c r="T66">
-        <v>2.588396754126687</v>
+        <v>2.654801747818839</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.293916229897955</v>
+        <v>3.243240595591833</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0928866960638791</v>
+        <v>0.09278735000872115</v>
       </c>
       <c r="C67">
-        <v>127.383962051161</v>
+        <v>124.3454972802429</v>
       </c>
       <c r="D67">
-        <v>312.883962051161</v>
+        <v>313.545497280243</v>
       </c>
       <c r="E67">
-        <v>86.5</v>
+        <v>90.20000000000002</v>
       </c>
       <c r="F67">
-        <v>240.5</v>
+        <v>244.2</v>
       </c>
       <c r="G67">
         <v>55</v>
@@ -6781,28 +6781,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M67">
-        <v>15.41605</v>
+        <v>15.65322</v>
       </c>
       <c r="N67">
-        <v>34.58190918367347</v>
+        <v>34.34473918367347</v>
       </c>
       <c r="O67">
-        <v>8.299658204081634</v>
+        <v>8.242737404081632</v>
       </c>
       <c r="P67">
-        <v>26.28225097959184</v>
+        <v>26.10200177959184</v>
       </c>
       <c r="Q67">
-        <v>61.18225097959184</v>
+        <v>61.00200177959184</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1749179887539403</v>
+        <v>0.1783376176727093</v>
       </c>
       <c r="T67">
-        <v>2.654801747818839</v>
+        <v>2.725112917610528</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.243240595591833</v>
+        <v>3.194100586567713</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09278735000872115</v>
+        <v>0.09268800395356319</v>
       </c>
       <c r="C68">
-        <v>124.3454972802429</v>
+        <v>121.3098358240245</v>
       </c>
       <c r="D68">
-        <v>313.545497280243</v>
+        <v>314.2098358240245</v>
       </c>
       <c r="E68">
-        <v>90.20000000000002</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F68">
-        <v>244.2</v>
+        <v>247.9</v>
       </c>
       <c r="G68">
         <v>55</v>
@@ -6863,28 +6863,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M68">
-        <v>15.65322</v>
+        <v>15.89039</v>
       </c>
       <c r="N68">
-        <v>34.34473918367347</v>
+        <v>34.10756918367347</v>
       </c>
       <c r="O68">
-        <v>8.242737404081632</v>
+        <v>8.185816604081632</v>
       </c>
       <c r="P68">
-        <v>26.10200177959184</v>
+        <v>25.92175257959184</v>
       </c>
       <c r="Q68">
-        <v>61.00200177959184</v>
+        <v>60.82175257959184</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1783376176727093</v>
+        <v>0.1819644968289794</v>
       </c>
       <c r="T68">
-        <v>2.725112917610528</v>
+        <v>2.799685370419896</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.194100586567713</v>
+        <v>3.146427443484614</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09268800395356319</v>
+        <v>0.09258865789840524</v>
       </c>
       <c r="C69">
-        <v>121.3098358240245</v>
+        <v>118.2769955392855</v>
       </c>
       <c r="D69">
-        <v>314.2098358240245</v>
+        <v>314.8769955392855</v>
       </c>
       <c r="E69">
-        <v>93.90000000000001</v>
+        <v>97.60000000000002</v>
       </c>
       <c r="F69">
-        <v>247.9</v>
+        <v>251.6</v>
       </c>
       <c r="G69">
         <v>55</v>
@@ -6945,28 +6945,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M69">
-        <v>15.89039</v>
+        <v>16.12756</v>
       </c>
       <c r="N69">
-        <v>34.10756918367347</v>
+        <v>33.87039918367347</v>
       </c>
       <c r="O69">
-        <v>8.185816604081632</v>
+        <v>8.128895804081633</v>
       </c>
       <c r="P69">
-        <v>25.92175257959184</v>
+        <v>25.74150337959184</v>
       </c>
       <c r="Q69">
-        <v>60.82175257959184</v>
+        <v>60.64150337959184</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1819644968289794</v>
+        <v>0.1858180559325164</v>
       </c>
       <c r="T69">
-        <v>2.799685370419896</v>
+        <v>2.878918601529849</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.146427443484614</v>
+        <v>3.100156451668663</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09258865789840524</v>
+        <v>0.0924893118432473</v>
       </c>
       <c r="C70">
-        <v>118.2769955392855</v>
+        <v>115.2469944347894</v>
       </c>
       <c r="D70">
-        <v>314.8769955392855</v>
+        <v>315.5469944347894</v>
       </c>
       <c r="E70">
-        <v>97.60000000000002</v>
+        <v>101.3</v>
       </c>
       <c r="F70">
-        <v>251.6</v>
+        <v>255.3</v>
       </c>
       <c r="G70">
         <v>55</v>
@@ -7027,28 +7027,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M70">
-        <v>16.12756</v>
+        <v>16.36473</v>
       </c>
       <c r="N70">
-        <v>33.87039918367347</v>
+        <v>33.63322918367347</v>
       </c>
       <c r="O70">
-        <v>8.128895804081633</v>
+        <v>8.071975004081633</v>
       </c>
       <c r="P70">
-        <v>25.74150337959184</v>
+        <v>25.56125417959184</v>
       </c>
       <c r="Q70">
-        <v>60.64150337959184</v>
+        <v>60.46125417959185</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1858180559325164</v>
+        <v>0.1899202317524107</v>
       </c>
       <c r="T70">
-        <v>2.878918601529849</v>
+        <v>2.963263654001735</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.100156451668663</v>
+        <v>3.055226648021292</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0924893118432473</v>
+        <v>0.09238996578808935</v>
       </c>
       <c r="C71">
-        <v>115.2469944347894</v>
+        <v>112.2198506729036</v>
       </c>
       <c r="D71">
-        <v>315.5469944347894</v>
+        <v>316.2198506729036</v>
       </c>
       <c r="E71">
-        <v>101.3</v>
+        <v>105</v>
       </c>
       <c r="F71">
-        <v>255.3</v>
+        <v>259</v>
       </c>
       <c r="G71">
         <v>55</v>
@@ -7109,28 +7109,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M71">
-        <v>16.36473</v>
+        <v>16.6019</v>
       </c>
       <c r="N71">
-        <v>33.63322918367347</v>
+        <v>33.39605918367347</v>
       </c>
       <c r="O71">
-        <v>8.071975004081633</v>
+        <v>8.015054204081633</v>
       </c>
       <c r="P71">
-        <v>25.56125417959184</v>
+        <v>25.38100497959184</v>
       </c>
       <c r="Q71">
-        <v>60.46125417959185</v>
+        <v>60.28100497959184</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1899202317524107</v>
+        <v>0.1942958859602978</v>
       </c>
       <c r="T71">
-        <v>2.963263654001735</v>
+        <v>3.053231709971746</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.055226648021292</v>
+        <v>3.011580553049559</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09238996578808935</v>
+        <v>0.0964994997329314</v>
       </c>
       <c r="C72">
-        <v>112.2198506729036</v>
+        <v>82.88811432010692</v>
       </c>
       <c r="D72">
-        <v>316.2198506729036</v>
+        <v>290.588114320107</v>
       </c>
       <c r="E72">
-        <v>105</v>
+        <v>108.7</v>
       </c>
       <c r="F72">
-        <v>259</v>
+        <v>262.7</v>
       </c>
       <c r="G72">
         <v>55</v>
@@ -7191,45 +7191,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M72">
-        <v>16.6019</v>
+        <v>18.88813</v>
       </c>
       <c r="N72">
-        <v>33.39605918367347</v>
+        <v>31.10982918367347</v>
       </c>
       <c r="O72">
-        <v>8.015054204081633</v>
+        <v>7.466359004081633</v>
       </c>
       <c r="P72">
-        <v>25.38100497959184</v>
+        <v>23.64347017959184</v>
       </c>
       <c r="Q72">
-        <v>60.28100497959184</v>
+        <v>58.54347017959184</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1942958859602978</v>
+        <v>0.1989733094239014</v>
       </c>
       <c r="T72">
-        <v>3.053231709971746</v>
+        <v>3.14940445945693</v>
       </c>
       <c r="U72">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.24</v>
       </c>
       <c r="W72">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.011580553049559</v>
+        <v>2.647057129725042</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0964994997329314</v>
+        <v>0.09645943367777345</v>
       </c>
       <c r="C73">
-        <v>82.88811432010698</v>
+        <v>79.41793764364928</v>
       </c>
       <c r="D73">
-        <v>290.588114320107</v>
+        <v>290.8179376436493</v>
       </c>
       <c r="E73">
-        <v>108.7</v>
+        <v>112.4</v>
       </c>
       <c r="F73">
-        <v>262.7</v>
+        <v>266.4</v>
       </c>
       <c r="G73">
         <v>55</v>
@@ -7273,28 +7273,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M73">
-        <v>18.88813</v>
+        <v>19.15416</v>
       </c>
       <c r="N73">
-        <v>31.10982918367347</v>
+        <v>30.84379918367347</v>
       </c>
       <c r="O73">
-        <v>7.466359004081633</v>
+        <v>7.402511804081633</v>
       </c>
       <c r="P73">
-        <v>23.64347017959184</v>
+        <v>23.44128737959184</v>
       </c>
       <c r="Q73">
-        <v>58.54347017959184</v>
+        <v>58.34128737959185</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1989733094239014</v>
+        <v>0.2039848345634766</v>
       </c>
       <c r="T73">
-        <v>3.149404459456929</v>
+        <v>3.252446691048198</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.647057129725042</v>
+        <v>2.61029244736775</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09645943367777345</v>
+        <v>0.09641936762261549</v>
       </c>
       <c r="C74">
-        <v>79.41793764364928</v>
+        <v>75.94812478501029</v>
       </c>
       <c r="D74">
-        <v>290.8179376436493</v>
+        <v>291.0481247850103</v>
       </c>
       <c r="E74">
-        <v>112.4</v>
+        <v>116.1</v>
       </c>
       <c r="F74">
-        <v>266.4</v>
+        <v>270.1</v>
       </c>
       <c r="G74">
         <v>55</v>
@@ -7355,28 +7355,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M74">
-        <v>19.15416</v>
+        <v>19.42019</v>
       </c>
       <c r="N74">
-        <v>30.84379918367347</v>
+        <v>30.57776918367347</v>
       </c>
       <c r="O74">
-        <v>7.402511804081633</v>
+        <v>7.338664604081633</v>
       </c>
       <c r="P74">
-        <v>23.44128737959184</v>
+        <v>23.23910457959184</v>
       </c>
       <c r="Q74">
-        <v>58.34128737959185</v>
+        <v>58.13910457959184</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2039848345634766</v>
+        <v>0.2093675837874648</v>
       </c>
       <c r="T74">
-        <v>3.252446691048198</v>
+        <v>3.363121680535116</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.61029244736775</v>
+        <v>2.574535016581891</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09641936762261549</v>
+        <v>0.09637930156745754</v>
       </c>
       <c r="C75">
-        <v>75.94812478501029</v>
+        <v>72.47867660877756</v>
       </c>
       <c r="D75">
-        <v>291.0481247850103</v>
+        <v>291.2786766087776</v>
       </c>
       <c r="E75">
-        <v>116.1</v>
+        <v>119.8</v>
       </c>
       <c r="F75">
-        <v>270.1</v>
+        <v>273.8</v>
       </c>
       <c r="G75">
         <v>55</v>
@@ -7437,28 +7437,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M75">
-        <v>19.42019</v>
+        <v>19.68622</v>
       </c>
       <c r="N75">
-        <v>30.57776918367347</v>
+        <v>30.31173918367347</v>
       </c>
       <c r="O75">
-        <v>7.338664604081633</v>
+        <v>7.274817404081633</v>
       </c>
       <c r="P75">
-        <v>23.23910457959184</v>
+        <v>23.03692177959184</v>
       </c>
       <c r="Q75">
-        <v>58.13910457959184</v>
+        <v>57.93692177959184</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2093675837874648</v>
+        <v>0.2151643906440674</v>
       </c>
       <c r="T75">
-        <v>3.363121680535116</v>
+        <v>3.482310130751797</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.574535016581891</v>
+        <v>2.539744002844297</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09637930156745754</v>
+        <v>0.0963392355122996</v>
       </c>
       <c r="C76">
-        <v>72.47867660877756</v>
+        <v>69.00959398228036</v>
       </c>
       <c r="D76">
-        <v>291.2786766087776</v>
+        <v>291.5095939822804</v>
       </c>
       <c r="E76">
-        <v>119.8</v>
+        <v>123.5</v>
       </c>
       <c r="F76">
-        <v>273.8</v>
+        <v>277.5</v>
       </c>
       <c r="G76">
         <v>55</v>
@@ -7519,28 +7519,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M76">
-        <v>19.68622</v>
+        <v>19.95225</v>
       </c>
       <c r="N76">
-        <v>30.31173918367347</v>
+        <v>30.04570918367347</v>
       </c>
       <c r="O76">
-        <v>7.274817404081633</v>
+        <v>7.210970204081632</v>
       </c>
       <c r="P76">
-        <v>23.03692177959184</v>
+        <v>22.83473897959184</v>
       </c>
       <c r="Q76">
-        <v>57.93692177959184</v>
+        <v>57.73473897959184</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2151643906440674</v>
+        <v>0.2214249420491984</v>
       </c>
       <c r="T76">
-        <v>3.482310130751797</v>
+        <v>3.611033656985814</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.539744002844297</v>
+        <v>2.50588074947304</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0963392355122996</v>
+        <v>0.09855180945714165</v>
       </c>
       <c r="C77">
-        <v>69.00959398228036</v>
+        <v>53.08278055248331</v>
       </c>
       <c r="D77">
-        <v>291.5095939822804</v>
+        <v>279.2827805524833</v>
       </c>
       <c r="E77">
-        <v>123.5</v>
+        <v>127.2</v>
       </c>
       <c r="F77">
-        <v>277.5</v>
+        <v>281.2</v>
       </c>
       <c r="G77">
         <v>55</v>
@@ -7601,45 +7601,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M77">
-        <v>19.95225</v>
+        <v>21.31496</v>
       </c>
       <c r="N77">
-        <v>30.04570918367347</v>
+        <v>28.68299918367347</v>
       </c>
       <c r="O77">
-        <v>7.210970204081632</v>
+        <v>6.883919804081633</v>
       </c>
       <c r="P77">
-        <v>22.83473897959184</v>
+        <v>21.79907937959184</v>
       </c>
       <c r="Q77">
-        <v>57.73473897959184</v>
+        <v>56.69907937959185</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2214249420491984</v>
+        <v>0.2282072060714235</v>
       </c>
       <c r="T77">
-        <v>3.611033656985814</v>
+        <v>3.750484143739331</v>
       </c>
       <c r="U77">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.24</v>
       </c>
       <c r="W77">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.50588074947304</v>
+        <v>2.345674548939969</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09855180945714165</v>
+        <v>0.09854138340198371</v>
       </c>
       <c r="C78">
-        <v>53.08278055248331</v>
+        <v>49.43798990587675</v>
       </c>
       <c r="D78">
-        <v>279.2827805524833</v>
+        <v>279.3379899058768</v>
       </c>
       <c r="E78">
-        <v>127.2</v>
+        <v>130.9</v>
       </c>
       <c r="F78">
-        <v>281.2</v>
+        <v>284.9</v>
       </c>
       <c r="G78">
         <v>55</v>
@@ -7683,28 +7683,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M78">
-        <v>21.31496</v>
+        <v>21.59542</v>
       </c>
       <c r="N78">
-        <v>28.68299918367347</v>
+        <v>28.40253918367347</v>
       </c>
       <c r="O78">
-        <v>6.883919804081633</v>
+        <v>6.816609404081632</v>
       </c>
       <c r="P78">
-        <v>21.79907937959184</v>
+        <v>21.58592977959184</v>
       </c>
       <c r="Q78">
-        <v>56.69907937959185</v>
+        <v>56.48592977959184</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2282072060714235</v>
+        <v>0.2355792321825378</v>
       </c>
       <c r="T78">
-        <v>3.750484143739331</v>
+        <v>3.902060759775763</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.345674548939969</v>
+        <v>2.315211243109579</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09854138340198371</v>
+        <v>0.09853095734682575</v>
       </c>
       <c r="C79">
-        <v>49.43798990587675</v>
+        <v>45.79322109144613</v>
       </c>
       <c r="D79">
-        <v>279.3379899058768</v>
+        <v>279.3932210914462</v>
       </c>
       <c r="E79">
-        <v>130.9</v>
+        <v>134.6</v>
       </c>
       <c r="F79">
-        <v>284.9</v>
+        <v>288.6</v>
       </c>
       <c r="G79">
         <v>55</v>
@@ -7765,28 +7765,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M79">
-        <v>21.59542</v>
+        <v>21.87588</v>
       </c>
       <c r="N79">
-        <v>28.40253918367347</v>
+        <v>28.12207918367347</v>
       </c>
       <c r="O79">
-        <v>6.816609404081632</v>
+        <v>6.749299004081633</v>
       </c>
       <c r="P79">
-        <v>21.58592977959184</v>
+        <v>21.37278017959184</v>
       </c>
       <c r="Q79">
-        <v>56.48592977959184</v>
+        <v>56.27278017959185</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2355792321825378</v>
+        <v>0.2436214424855716</v>
       </c>
       <c r="T79">
-        <v>3.902060759775763</v>
+        <v>4.067417068179143</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.315211243109579</v>
+        <v>2.285529047685097</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09853095734682575</v>
+        <v>0.0985205312916678</v>
       </c>
       <c r="C80">
-        <v>45.79322109144613</v>
+        <v>42.14847412214385</v>
       </c>
       <c r="D80">
-        <v>279.3932210914462</v>
+        <v>279.4484741221439</v>
       </c>
       <c r="E80">
-        <v>134.6</v>
+        <v>138.3</v>
       </c>
       <c r="F80">
-        <v>288.6</v>
+        <v>292.3</v>
       </c>
       <c r="G80">
         <v>55</v>
@@ -7847,28 +7847,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M80">
-        <v>21.87588</v>
+        <v>22.15634</v>
       </c>
       <c r="N80">
-        <v>28.12207918367347</v>
+        <v>27.84161918367347</v>
       </c>
       <c r="O80">
-        <v>6.749299004081633</v>
+        <v>6.681988604081632</v>
       </c>
       <c r="P80">
-        <v>21.37278017959184</v>
+        <v>21.15963057959184</v>
       </c>
       <c r="Q80">
-        <v>56.27278017959185</v>
+        <v>56.05963057959184</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2436214424855716</v>
+        <v>0.2524295775793705</v>
       </c>
       <c r="T80">
-        <v>4.067417068179143</v>
+        <v>4.248521596430464</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.285529047685097</v>
+        <v>2.256598300246045</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0985205312916678</v>
+        <v>0.09851010523650984</v>
       </c>
       <c r="C81">
-        <v>42.14847412214385</v>
+        <v>38.50374901093284</v>
       </c>
       <c r="D81">
-        <v>279.4484741221439</v>
+        <v>279.5037490109328</v>
       </c>
       <c r="E81">
-        <v>138.3</v>
+        <v>142</v>
       </c>
       <c r="F81">
-        <v>292.3</v>
+        <v>296</v>
       </c>
       <c r="G81">
         <v>55</v>
@@ -7929,28 +7929,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M81">
-        <v>22.15634</v>
+        <v>22.4368</v>
       </c>
       <c r="N81">
-        <v>27.84161918367347</v>
+        <v>27.56115918367347</v>
       </c>
       <c r="O81">
-        <v>6.681988604081632</v>
+        <v>6.614678204081633</v>
       </c>
       <c r="P81">
-        <v>21.15963057959184</v>
+        <v>20.94648097959184</v>
       </c>
       <c r="Q81">
-        <v>56.05963057959184</v>
+        <v>55.84648097959185</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2524295775793705</v>
+        <v>0.2621185261825492</v>
       </c>
       <c r="T81">
-        <v>4.248521596430464</v>
+        <v>4.447736577506918</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.256598300246045</v>
+        <v>2.22839082149297</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09851010523650984</v>
+        <v>0.09849967918135188</v>
       </c>
       <c r="C82">
-        <v>38.50374901093284</v>
+        <v>34.85904577078622</v>
       </c>
       <c r="D82">
-        <v>279.5037490109328</v>
+        <v>279.5590457707863</v>
       </c>
       <c r="E82">
-        <v>142</v>
+        <v>145.7</v>
       </c>
       <c r="F82">
-        <v>296</v>
+        <v>299.7</v>
       </c>
       <c r="G82">
         <v>55</v>
@@ -8011,28 +8011,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M82">
-        <v>22.4368</v>
+        <v>22.71726000000001</v>
       </c>
       <c r="N82">
-        <v>27.56115918367347</v>
+        <v>27.28069918367347</v>
       </c>
       <c r="O82">
-        <v>6.614678204081633</v>
+        <v>6.547367804081632</v>
       </c>
       <c r="P82">
-        <v>20.94648097959184</v>
+        <v>20.73333137959184</v>
       </c>
       <c r="Q82">
-        <v>55.84648097959185</v>
+        <v>55.63333137959184</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2621185261825492</v>
+        <v>0.2728273641123784</v>
       </c>
       <c r="T82">
-        <v>4.447736577506918</v>
+        <v>4.667921556591419</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.22839082149297</v>
+        <v>2.20087982369676</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09849967918135188</v>
+        <v>0.09848925312619394</v>
       </c>
       <c r="C83">
-        <v>34.85904577078622</v>
+        <v>31.2143644146874</v>
       </c>
       <c r="D83">
-        <v>279.5590457707863</v>
+        <v>279.6143644146874</v>
       </c>
       <c r="E83">
-        <v>145.7</v>
+        <v>149.4</v>
       </c>
       <c r="F83">
-        <v>299.7</v>
+        <v>303.4</v>
       </c>
       <c r="G83">
         <v>55</v>
@@ -8093,28 +8093,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M83">
-        <v>22.71726000000001</v>
+        <v>22.99772</v>
       </c>
       <c r="N83">
-        <v>27.28069918367347</v>
+        <v>27.00023918367347</v>
       </c>
       <c r="O83">
-        <v>6.547367804081632</v>
+        <v>6.480057404081632</v>
       </c>
       <c r="P83">
-        <v>20.73333137959184</v>
+        <v>20.52018177959184</v>
       </c>
       <c r="Q83">
-        <v>55.63333137959184</v>
+        <v>55.42018177959184</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2728273641123784</v>
+        <v>0.2847260729232998</v>
       </c>
       <c r="T83">
-        <v>4.667921556591419</v>
+        <v>4.912571533351976</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.20087982369676</v>
+        <v>2.174039825846799</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09848925312619394</v>
+        <v>0.098478827071036</v>
       </c>
       <c r="C84">
-        <v>31.2143644146874</v>
+        <v>27.56970495563019</v>
       </c>
       <c r="D84">
-        <v>279.6143644146874</v>
+        <v>279.6697049556302</v>
       </c>
       <c r="E84">
-        <v>149.4</v>
+        <v>153.1</v>
       </c>
       <c r="F84">
-        <v>303.4</v>
+        <v>307.1</v>
       </c>
       <c r="G84">
         <v>55</v>
@@ -8175,28 +8175,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M84">
-        <v>22.99772</v>
+        <v>23.27818</v>
       </c>
       <c r="N84">
-        <v>27.00023918367347</v>
+        <v>26.71977918367347</v>
       </c>
       <c r="O84">
-        <v>6.480057404081632</v>
+        <v>6.412747004081632</v>
       </c>
       <c r="P84">
-        <v>20.52018177959184</v>
+        <v>20.30703217959184</v>
       </c>
       <c r="Q84">
-        <v>55.42018177959184</v>
+        <v>55.20703217959184</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2847260729232998</v>
+        <v>0.2980246298296236</v>
       </c>
       <c r="T84">
-        <v>4.912571533351976</v>
+        <v>5.186003860319657</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.174039825846799</v>
+        <v>2.147846574932983</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.098478827071036</v>
+        <v>0.09846840101587805</v>
       </c>
       <c r="C85">
-        <v>27.56970495563019</v>
+        <v>23.92506740661855</v>
       </c>
       <c r="D85">
-        <v>279.6697049556302</v>
+        <v>279.7250674066186</v>
       </c>
       <c r="E85">
-        <v>153.1</v>
+        <v>156.8</v>
       </c>
       <c r="F85">
-        <v>307.1</v>
+        <v>310.8</v>
       </c>
       <c r="G85">
         <v>55</v>
@@ -8257,28 +8257,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M85">
-        <v>23.27818</v>
+        <v>23.55864</v>
       </c>
       <c r="N85">
-        <v>26.71977918367347</v>
+        <v>26.43931918367347</v>
       </c>
       <c r="O85">
-        <v>6.412747004081632</v>
+        <v>6.345436604081632</v>
       </c>
       <c r="P85">
-        <v>20.30703217959184</v>
+        <v>20.09388257959183</v>
       </c>
       <c r="Q85">
-        <v>55.20703217959184</v>
+        <v>54.99388257959184</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2980246298296236</v>
+        <v>0.3129855063492379</v>
       </c>
       <c r="T85">
-        <v>5.186003860319657</v>
+        <v>5.493615228158299</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.147846574932983</v>
+        <v>2.122276972850448</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09846840101587806</v>
+        <v>0.09845797496072012</v>
       </c>
       <c r="C86">
-        <v>23.92506740661844</v>
+        <v>20.28045178066657</v>
       </c>
       <c r="D86">
-        <v>279.7250674066185</v>
+        <v>279.7804517806666</v>
       </c>
       <c r="E86">
-        <v>156.8</v>
+        <v>160.5</v>
       </c>
       <c r="F86">
-        <v>310.8</v>
+        <v>314.5</v>
       </c>
       <c r="G86">
         <v>55</v>
@@ -8339,28 +8339,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M86">
-        <v>23.55864</v>
+        <v>23.8391</v>
       </c>
       <c r="N86">
-        <v>26.43931918367347</v>
+        <v>26.15885918367347</v>
       </c>
       <c r="O86">
-        <v>6.345436604081632</v>
+        <v>6.278126204081633</v>
       </c>
       <c r="P86">
-        <v>20.09388257959183</v>
+        <v>19.88073297959184</v>
       </c>
       <c r="Q86">
-        <v>54.99388257959184</v>
+        <v>54.78073297959185</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3129855063492377</v>
+        <v>0.3299411664048006</v>
       </c>
       <c r="T86">
-        <v>5.493615228158295</v>
+        <v>5.842241445042089</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.122276972850448</v>
+        <v>2.097309008463972</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09845797496072012</v>
+        <v>0.09844754890556215</v>
       </c>
       <c r="C87">
-        <v>20.28045178066657</v>
+        <v>16.63585809079922</v>
       </c>
       <c r="D87">
-        <v>279.7804517806666</v>
+        <v>279.8358580907992</v>
       </c>
       <c r="E87">
-        <v>160.5</v>
+        <v>164.2</v>
       </c>
       <c r="F87">
-        <v>314.5</v>
+        <v>318.2</v>
       </c>
       <c r="G87">
         <v>55</v>
@@ -8421,28 +8421,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M87">
-        <v>23.8391</v>
+        <v>24.11956</v>
       </c>
       <c r="N87">
-        <v>26.15885918367347</v>
+        <v>25.87839918367347</v>
       </c>
       <c r="O87">
-        <v>6.278126204081633</v>
+        <v>6.210815804081633</v>
       </c>
       <c r="P87">
-        <v>19.88073297959184</v>
+        <v>19.66758337959184</v>
       </c>
       <c r="Q87">
-        <v>54.78073297959185</v>
+        <v>54.56758337959185</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3299411664048006</v>
+        <v>0.3493190636111582</v>
       </c>
       <c r="T87">
-        <v>5.842241445042089</v>
+        <v>6.240671407194995</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.097309008463972</v>
+        <v>2.072921694412065</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09844754890556215</v>
+        <v>0.09843712285040419</v>
       </c>
       <c r="C88">
-        <v>16.63585809079922</v>
+        <v>12.99128635005121</v>
       </c>
       <c r="D88">
-        <v>279.8358580907992</v>
+        <v>279.8912863500512</v>
       </c>
       <c r="E88">
-        <v>164.2</v>
+        <v>167.9</v>
       </c>
       <c r="F88">
-        <v>318.2</v>
+        <v>321.9</v>
       </c>
       <c r="G88">
         <v>55</v>
@@ -8503,28 +8503,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M88">
-        <v>24.11956</v>
+        <v>24.40002</v>
       </c>
       <c r="N88">
-        <v>25.87839918367347</v>
+        <v>25.59793918367347</v>
       </c>
       <c r="O88">
-        <v>6.210815804081633</v>
+        <v>6.143505404081633</v>
       </c>
       <c r="P88">
-        <v>19.66758337959184</v>
+        <v>19.45443377959184</v>
       </c>
       <c r="Q88">
-        <v>54.56758337959185</v>
+        <v>54.35443377959184</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3493190636111582</v>
+        <v>0.3716781757723399</v>
       </c>
       <c r="T88">
-        <v>6.240671407194995</v>
+        <v>6.700398286602194</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.072921694412065</v>
+        <v>2.049095008269398</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09843712285040419</v>
+        <v>0.09842669679524625</v>
       </c>
       <c r="C89">
-        <v>12.99128635005121</v>
+        <v>9.346736571467602</v>
       </c>
       <c r="D89">
-        <v>279.8912863500512</v>
+        <v>279.9467365714676</v>
       </c>
       <c r="E89">
-        <v>167.9</v>
+        <v>171.6</v>
       </c>
       <c r="F89">
-        <v>321.9</v>
+        <v>325.6</v>
       </c>
       <c r="G89">
         <v>55</v>
@@ -8585,28 +8585,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M89">
-        <v>24.40002</v>
+        <v>24.68048</v>
       </c>
       <c r="N89">
-        <v>25.59793918367347</v>
+        <v>25.31747918367347</v>
       </c>
       <c r="O89">
-        <v>6.143505404081633</v>
+        <v>6.076195004081632</v>
       </c>
       <c r="P89">
-        <v>19.45443377959184</v>
+        <v>19.24128417959184</v>
       </c>
       <c r="Q89">
-        <v>54.35443377959184</v>
+        <v>54.14128417959184</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3716781757723399</v>
+        <v>0.3977638066270521</v>
       </c>
       <c r="T89">
-        <v>6.700398286602194</v>
+        <v>7.236746312577262</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.049095008269398</v>
+        <v>2.025809837720882</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09842669679524625</v>
+        <v>0.0984162707400883</v>
       </c>
       <c r="C90">
-        <v>9.346736571467602</v>
+        <v>5.702208768104356</v>
       </c>
       <c r="D90">
-        <v>279.9467365714676</v>
+        <v>280.0022087681044</v>
       </c>
       <c r="E90">
-        <v>171.6</v>
+        <v>175.3</v>
       </c>
       <c r="F90">
-        <v>325.6</v>
+        <v>329.3</v>
       </c>
       <c r="G90">
         <v>55</v>
@@ -8667,28 +8667,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M90">
-        <v>24.68048</v>
+        <v>24.96094</v>
       </c>
       <c r="N90">
-        <v>25.31747918367347</v>
+        <v>25.03701918367347</v>
       </c>
       <c r="O90">
-        <v>6.076195004081632</v>
+        <v>6.008884604081632</v>
       </c>
       <c r="P90">
-        <v>19.24128417959184</v>
+        <v>19.02813457959184</v>
       </c>
       <c r="Q90">
-        <v>54.14128417959184</v>
+        <v>53.92813457959184</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3977638066270521</v>
+        <v>0.4285922794553481</v>
       </c>
       <c r="T90">
-        <v>7.236746312577262</v>
+        <v>7.870612161456885</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.025809837720882</v>
+        <v>2.003047929431883</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0984162707400883</v>
+        <v>0.1081186446849303</v>
       </c>
       <c r="C91">
-        <v>5.702208768104356</v>
+        <v>-41.59126391707457</v>
       </c>
       <c r="D91">
-        <v>280.0022087681044</v>
+        <v>236.4087360829254</v>
       </c>
       <c r="E91">
-        <v>175.3</v>
+        <v>179</v>
       </c>
       <c r="F91">
-        <v>329.3</v>
+        <v>333</v>
       </c>
       <c r="G91">
         <v>55</v>
@@ -8749,45 +8749,45 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M91">
-        <v>24.96094</v>
+        <v>29.97</v>
       </c>
       <c r="N91">
-        <v>25.03701918367347</v>
+        <v>20.02795918367347</v>
       </c>
       <c r="O91">
-        <v>6.008884604081632</v>
+        <v>4.806710204081633</v>
       </c>
       <c r="P91">
-        <v>19.02813457959184</v>
+        <v>15.22124897959184</v>
       </c>
       <c r="Q91">
-        <v>53.92813457959184</v>
+        <v>50.12124897959185</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4285922794553481</v>
+        <v>0.4655864468493035</v>
       </c>
       <c r="T91">
-        <v>7.870612161456885</v>
+        <v>8.631251180112434</v>
       </c>
       <c r="U91">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V91">
         <v>0.24</v>
       </c>
       <c r="W91">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.003047929431883</v>
+        <v>1.668266906362144</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1081186446849303</v>
+        <v>0.1082161386297724</v>
       </c>
       <c r="C92">
-        <v>-41.59126391707457</v>
+        <v>-45.66053412157345</v>
       </c>
       <c r="D92">
-        <v>236.4087360829254</v>
+        <v>236.0394658784266</v>
       </c>
       <c r="E92">
-        <v>179</v>
+        <v>182.7</v>
       </c>
       <c r="F92">
-        <v>333</v>
+        <v>336.7</v>
       </c>
       <c r="G92">
         <v>55</v>
@@ -8831,28 +8831,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M92">
-        <v>29.97</v>
+        <v>30.303</v>
       </c>
       <c r="N92">
-        <v>20.02795918367347</v>
+        <v>19.69495918367348</v>
       </c>
       <c r="O92">
-        <v>4.806710204081633</v>
+        <v>4.726790204081634</v>
       </c>
       <c r="P92">
-        <v>15.22124897959184</v>
+        <v>14.96816897959184</v>
       </c>
       <c r="Q92">
-        <v>50.12124897959185</v>
+        <v>49.86816897959184</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4655864468493035</v>
+        <v>0.5108015403308045</v>
       </c>
       <c r="T92">
-        <v>8.631251180112434</v>
+        <v>9.56092109180255</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.668266906362144</v>
+        <v>1.649934302995528</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1082161386297724</v>
+        <v>0.1083136325746144</v>
       </c>
       <c r="C93">
-        <v>-45.66053412157345</v>
+        <v>-49.72865252581806</v>
       </c>
       <c r="D93">
-        <v>236.0394658784266</v>
+        <v>235.671347474182</v>
       </c>
       <c r="E93">
-        <v>182.7</v>
+        <v>186.4</v>
       </c>
       <c r="F93">
-        <v>336.7</v>
+        <v>340.4</v>
       </c>
       <c r="G93">
         <v>55</v>
@@ -8913,28 +8913,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M93">
-        <v>30.303</v>
+        <v>30.636</v>
       </c>
       <c r="N93">
-        <v>19.69495918367348</v>
+        <v>19.36195918367347</v>
       </c>
       <c r="O93">
-        <v>4.726790204081634</v>
+        <v>4.646870204081632</v>
       </c>
       <c r="P93">
-        <v>14.96816897959184</v>
+        <v>14.71508897959184</v>
       </c>
       <c r="Q93">
-        <v>49.86816897959184</v>
+        <v>49.61508897959185</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5108015403308045</v>
+        <v>0.5673204071826807</v>
       </c>
       <c r="T93">
-        <v>9.56092109180255</v>
+        <v>10.7230084814152</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.649934302995528</v>
+        <v>1.632000234484706</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1083136325746144</v>
+        <v>0.1084111265194565</v>
       </c>
       <c r="C94">
-        <v>-49.72865252581806</v>
+        <v>-53.79562451033195</v>
       </c>
       <c r="D94">
-        <v>235.671347474182</v>
+        <v>235.3043754896681</v>
       </c>
       <c r="E94">
-        <v>186.4</v>
+        <v>190.1</v>
       </c>
       <c r="F94">
-        <v>340.4</v>
+        <v>344.1</v>
       </c>
       <c r="G94">
         <v>55</v>
@@ -8995,28 +8995,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M94">
-        <v>30.636</v>
+        <v>30.969</v>
       </c>
       <c r="N94">
-        <v>19.36195918367347</v>
+        <v>19.02895918367347</v>
       </c>
       <c r="O94">
-        <v>4.646870204081632</v>
+        <v>4.566950204081633</v>
       </c>
       <c r="P94">
-        <v>14.71508897959184</v>
+        <v>14.46200897959184</v>
       </c>
       <c r="Q94">
-        <v>49.61508897959185</v>
+        <v>49.36200897959185</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5673204071826807</v>
+        <v>0.6399875217065216</v>
       </c>
       <c r="T94">
-        <v>10.7230084814152</v>
+        <v>12.2171208394886</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.632000234484706</v>
+        <v>1.614451844866591</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1084111265194565</v>
+        <v>0.1085086204642985</v>
       </c>
       <c r="C95">
-        <v>-53.79562451033195</v>
+        <v>-57.86145542217838</v>
       </c>
       <c r="D95">
-        <v>235.3043754896681</v>
+        <v>234.9385445778217</v>
       </c>
       <c r="E95">
-        <v>190.1</v>
+        <v>193.8</v>
       </c>
       <c r="F95">
-        <v>344.1</v>
+        <v>347.8</v>
       </c>
       <c r="G95">
         <v>55</v>
@@ -9077,28 +9077,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M95">
-        <v>30.969</v>
+        <v>31.302</v>
       </c>
       <c r="N95">
-        <v>19.02895918367347</v>
+        <v>18.69595918367347</v>
       </c>
       <c r="O95">
-        <v>4.566950204081633</v>
+        <v>4.487030204081633</v>
       </c>
       <c r="P95">
-        <v>14.46200897959184</v>
+        <v>14.20892897959184</v>
       </c>
       <c r="Q95">
-        <v>49.36200897959185</v>
+        <v>49.10892897959184</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6399875217065216</v>
+        <v>0.7368770077383096</v>
       </c>
       <c r="T95">
-        <v>12.2171208394886</v>
+        <v>14.20927065025313</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.614451844866591</v>
+        <v>1.597276825240351</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1085086204642985</v>
+        <v>0.1086061144091406</v>
       </c>
       <c r="C96">
-        <v>-57.86145542217838</v>
+        <v>-61.92615057521914</v>
       </c>
       <c r="D96">
-        <v>234.9385445778217</v>
+        <v>234.5738494247808</v>
       </c>
       <c r="E96">
-        <v>193.8</v>
+        <v>197.5</v>
       </c>
       <c r="F96">
-        <v>347.8</v>
+        <v>351.5</v>
       </c>
       <c r="G96">
         <v>55</v>
@@ -9159,28 +9159,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M96">
-        <v>31.302</v>
+        <v>31.635</v>
       </c>
       <c r="N96">
-        <v>18.69595918367347</v>
+        <v>18.36295918367347</v>
       </c>
       <c r="O96">
-        <v>4.487030204081633</v>
+        <v>4.407110204081634</v>
       </c>
       <c r="P96">
-        <v>14.20892897959184</v>
+        <v>13.95584897959184</v>
       </c>
       <c r="Q96">
-        <v>49.10892897959184</v>
+        <v>48.85584897959185</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7368770077383096</v>
+        <v>0.872522288182813</v>
       </c>
       <c r="T96">
-        <v>14.20927065025313</v>
+        <v>16.99828038532349</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.597276825240351</v>
+        <v>1.580463384974663</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1086061144091406</v>
+        <v>0.1087036083539827</v>
       </c>
       <c r="C97">
-        <v>-61.92615057521914</v>
+        <v>-65.98971525037291</v>
       </c>
       <c r="D97">
-        <v>234.5738494247808</v>
+        <v>234.2102847496271</v>
       </c>
       <c r="E97">
-        <v>197.5</v>
+        <v>201.2</v>
       </c>
       <c r="F97">
-        <v>351.5</v>
+        <v>355.2</v>
       </c>
       <c r="G97">
         <v>55</v>
@@ -9241,28 +9241,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M97">
-        <v>31.635</v>
+        <v>31.968</v>
       </c>
       <c r="N97">
-        <v>18.36295918367347</v>
+        <v>18.02995918367347</v>
       </c>
       <c r="O97">
-        <v>4.407110204081634</v>
+        <v>4.327190204081632</v>
       </c>
       <c r="P97">
-        <v>13.95584897959184</v>
+        <v>13.70276897959184</v>
       </c>
       <c r="Q97">
-        <v>48.85584897959185</v>
+        <v>48.60276897959184</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.872522288182813</v>
+        <v>1.075990208849568</v>
       </c>
       <c r="T97">
-        <v>16.99828038532349</v>
+        <v>21.18179498792902</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.580463384974663</v>
+        <v>1.56400022471451</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1087036083539827</v>
+        <v>0.1088011022988247</v>
       </c>
       <c r="C98">
-        <v>-65.98971525037285</v>
+        <v>-70.05215469586881</v>
       </c>
       <c r="D98">
-        <v>234.2102847496271</v>
+        <v>233.8478453041312</v>
       </c>
       <c r="E98">
-        <v>201.2</v>
+        <v>204.9</v>
       </c>
       <c r="F98">
-        <v>355.2</v>
+        <v>358.9</v>
       </c>
       <c r="G98">
         <v>55</v>
@@ -9323,28 +9323,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M98">
-        <v>31.968</v>
+        <v>32.30099999999999</v>
       </c>
       <c r="N98">
-        <v>18.02995918367348</v>
+        <v>17.69695918367348</v>
       </c>
       <c r="O98">
-        <v>4.327190204081634</v>
+        <v>4.247270204081635</v>
       </c>
       <c r="P98">
-        <v>13.70276897959184</v>
+        <v>13.44968897959184</v>
       </c>
       <c r="Q98">
-        <v>48.60276897959184</v>
+        <v>48.34968897959185</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.075990208849565</v>
+        <v>1.415103409960822</v>
       </c>
       <c r="T98">
-        <v>21.18179498792896</v>
+        <v>28.15431932560482</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.564000224714511</v>
+        <v>1.54787651105766</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1088011022988247</v>
+        <v>0.1088985962436667</v>
       </c>
       <c r="C99">
-        <v>-70.05215469586881</v>
+        <v>-74.1134741275003</v>
       </c>
       <c r="D99">
-        <v>233.8478453041312</v>
+        <v>233.4865258724996</v>
       </c>
       <c r="E99">
-        <v>204.9</v>
+        <v>208.6</v>
       </c>
       <c r="F99">
-        <v>358.9</v>
+        <v>362.6</v>
       </c>
       <c r="G99">
         <v>55</v>
@@ -9405,28 +9405,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M99">
-        <v>32.30099999999999</v>
+        <v>32.63399999999999</v>
       </c>
       <c r="N99">
-        <v>17.69695918367348</v>
+        <v>17.36395918367348</v>
       </c>
       <c r="O99">
-        <v>4.247270204081635</v>
+        <v>4.167350204081635</v>
       </c>
       <c r="P99">
-        <v>13.44968897959184</v>
+        <v>13.19660897959184</v>
       </c>
       <c r="Q99">
-        <v>48.34968897959185</v>
+        <v>48.09660897959185</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.415103409960822</v>
+        <v>2.093329812183335</v>
       </c>
       <c r="T99">
-        <v>28.15431932560482</v>
+        <v>42.09936800095652</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.54787651105766</v>
+        <v>1.532081852781562</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1088985962436667</v>
+        <v>0.1089960901885088</v>
       </c>
       <c r="C100">
-        <v>-74.1134741275003</v>
+        <v>-78.17367872887479</v>
       </c>
       <c r="D100">
-        <v>233.4865258724996</v>
+        <v>233.1263212711252</v>
       </c>
       <c r="E100">
-        <v>208.6</v>
+        <v>212.3</v>
       </c>
       <c r="F100">
-        <v>362.6</v>
+        <v>366.3</v>
       </c>
       <c r="G100">
         <v>55</v>
@@ -9487,28 +9487,28 @@
         <v>49.99795918367347</v>
       </c>
       <c r="M100">
-        <v>32.63399999999999</v>
+        <v>32.967</v>
       </c>
       <c r="N100">
-        <v>17.36395918367348</v>
+        <v>17.03095918367347</v>
       </c>
       <c r="O100">
-        <v>4.167350204081635</v>
+        <v>4.087430204081634</v>
       </c>
       <c r="P100">
-        <v>13.19660897959184</v>
+        <v>12.94352897959184</v>
       </c>
       <c r="Q100">
-        <v>48.09660897959185</v>
+        <v>47.84352897959185</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.093329812183335</v>
+        <v>4.128009018850875</v>
       </c>
       <c r="T100">
-        <v>42.09936800095652</v>
+        <v>83.93451402701164</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.532081852781562</v>
+        <v>1.516606278511041</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1089960901885088</v>
-      </c>
-      <c r="C101">
-        <v>-78.17367872887479</v>
-      </c>
-      <c r="D101">
-        <v>233.1263212711252</v>
-      </c>
-      <c r="E101">
-        <v>212.3</v>
-      </c>
-      <c r="F101">
-        <v>366.3</v>
-      </c>
-      <c r="G101">
-        <v>55</v>
-      </c>
-      <c r="H101">
-        <v>216</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>84.89795918367348</v>
-      </c>
-      <c r="K101">
-        <v>34.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>49.99795918367347</v>
-      </c>
-      <c r="M101">
-        <v>32.967</v>
-      </c>
-      <c r="N101">
-        <v>17.03095918367347</v>
-      </c>
-      <c r="O101">
-        <v>4.087430204081634</v>
-      </c>
-      <c r="P101">
-        <v>12.94352897959184</v>
-      </c>
-      <c r="Q101">
-        <v>47.84352897959185</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.128009018850875</v>
-      </c>
-      <c r="T101">
-        <v>83.93451402701164</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.0684</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.516606278511041</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
